--- a/ptr_position.xlsx
+++ b/ptr_position.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,13 +459,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>43861</v>
+        <v>39478</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -474,21 +474,21 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>43890</v>
+        <v>39507</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -497,21 +497,21 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>43921</v>
+        <v>39538</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -520,21 +520,21 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>43951</v>
+        <v>39568</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -543,15 +543,15 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>43982</v>
+        <v>39599</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44012</v>
+        <v>39629</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44043</v>
+        <v>39660</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44074</v>
+        <v>39691</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44104</v>
+        <v>39721</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44135</v>
+        <v>39752</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44165</v>
+        <v>39782</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44196</v>
+        <v>39813</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44227</v>
+        <v>39844</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44255</v>
+        <v>39872</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -773,21 +773,21 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G15" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44286</v>
+        <v>39903</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -796,21 +796,21 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G16" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44316</v>
+        <v>39933</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -819,21 +819,21 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G17" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44347</v>
+        <v>39964</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -842,21 +842,21 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G18" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44377</v>
+        <v>39994</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -865,21 +865,21 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G19" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44408</v>
+        <v>40025</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -888,21 +888,21 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G20" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44439</v>
+        <v>40056</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -911,21 +911,21 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G21" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44469</v>
+        <v>40086</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -934,21 +934,21 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G22" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44500</v>
+        <v>40117</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -957,21 +957,21 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G23" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44530</v>
+        <v>40147</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -980,15 +980,15 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G24" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44561</v>
+        <v>40178</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>44592</v>
+        <v>40209</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>44620</v>
+        <v>40237</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1049,15 +1049,15 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G27" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>44651</v>
+        <v>40268</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -1080,13 +1080,13 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>44681</v>
+        <v>40298</v>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1095,21 +1095,21 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G29" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>44712</v>
+        <v>40329</v>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1118,21 +1118,21 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G30" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44742</v>
+        <v>40359</v>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1141,1067 +1141,4379 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="G31" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>44773</v>
+        <v>40390</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.09636835888532423</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.25</v>
+        <v>0.274092089721331</v>
       </c>
       <c r="G32" t="n">
-        <v>37.5</v>
+        <v>63.70460448606655</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>44804</v>
+        <v>40421</v>
       </c>
       <c r="B33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3753037679568214</v>
+        <v>0.02685913742639891</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3438259419892054</v>
+        <v>0.2567147843565997</v>
       </c>
       <c r="G33" t="n">
-        <v>32.80870290053974</v>
+        <v>62.83573921782999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>44834</v>
+        <v>40451</v>
       </c>
       <c r="B34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1807557520612843</v>
+        <v>-0.1844634646294006</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2048110619846789</v>
+        <v>0.2038841338426499</v>
       </c>
       <c r="G34" t="n">
-        <v>39.75944690076606</v>
+        <v>60.19420669213249</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>44865</v>
+        <v>40482</v>
       </c>
       <c r="B35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1822659137030626</v>
+        <v>-0.09478188099775604</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2044335215742344</v>
+        <v>0.226304529750561</v>
       </c>
       <c r="G35" t="n">
-        <v>39.77832392128828</v>
+        <v>61.31522648752805</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>44895</v>
+        <v>40512</v>
       </c>
       <c r="B36" t="n">
-        <v>-1</v>
+        <v>0.4523376763211556</v>
       </c>
       <c r="C36" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>-0.4523376763211556</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3044698743710083</v>
+        <v>0.06433217683865598</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.326117468592752</v>
+        <v>0.266083044209664</v>
       </c>
       <c r="G36" t="n">
-        <v>33.6941265703624</v>
+        <v>63.3041522104832</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>44926</v>
+        <v>40543</v>
       </c>
       <c r="B37" t="n">
-        <v>-1</v>
+        <v>0.6010085899255</v>
       </c>
       <c r="C37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>-0.6010085899255</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1084050470279523</v>
+        <v>-0.163089393680277</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2228987382430119</v>
+        <v>0.2092276515799308</v>
       </c>
       <c r="G37" t="n">
-        <v>38.85506308784941</v>
+        <v>60.46138257899653</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>44957</v>
+        <v>40574</v>
       </c>
       <c r="B38" t="n">
-        <v>-1</v>
+        <v>0.7871984460121464</v>
       </c>
       <c r="C38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>-0.7871984460121464</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3600820492838798</v>
+        <v>-0.4687098824166767</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.15997948767903</v>
+        <v>0.1328225293958308</v>
       </c>
       <c r="G38" t="n">
-        <v>42.0010256160485</v>
+        <v>56.64112646979154</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>44985</v>
+        <v>40602</v>
       </c>
       <c r="B39" t="n">
-        <v>-1</v>
+        <v>0.8426384288286446</v>
       </c>
       <c r="C39" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>-0.8426384288286446</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7339537065403337</v>
+        <v>-0.6176036998743041</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.06651157336491659</v>
+        <v>0.09559907503142398</v>
       </c>
       <c r="G39" t="n">
-        <v>46.67442133175417</v>
+        <v>54.7799537515712</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45016</v>
+        <v>40633</v>
       </c>
       <c r="B40" t="n">
-        <v>-1</v>
+        <v>0.5705924032910326</v>
       </c>
       <c r="C40" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>-0.5705924032910326</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>-0.5930598441786412</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.1017350389553397</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>55.08675194776698</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45046</v>
+        <v>40663</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.8054412078474431</v>
+        <v>0.6227152803736784</v>
       </c>
       <c r="C41" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8054412078474431</v>
+        <v>-0.6227152803736784</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>-0.7162154973329663</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.07094612566675843</v>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>53.54730628333792</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45077</v>
+        <v>40694</v>
       </c>
       <c r="B42" t="n">
-        <v>-0.6094477485128564</v>
+        <v>0.9364610312111221</v>
       </c>
       <c r="C42" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6094477485128564</v>
+        <v>-0.9364610312111221</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>-0.9576335175185765</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.01059162062035587</v>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>50.52958103101779</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45107</v>
+        <v>40724</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1977070230233739</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1977070230233739</v>
+        <v>-1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>-0.8748760156265414</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.03128099609336465</v>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>51.56404980466823</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45138</v>
+        <v>40755</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.1475652529778815</v>
+        <v>0.6015587045419569</v>
       </c>
       <c r="C44" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1475652529778815</v>
+        <v>-0.6015587045419569</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7565542369561112</v>
+        <v>-0.6587910731314257</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.06086144076097219</v>
+        <v>0.08530223171714357</v>
       </c>
       <c r="G44" t="n">
-        <v>46.95692796195139</v>
+        <v>54.26511158585718</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45169</v>
+        <v>40786</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.01541875522536249</v>
+        <v>0.4809077360151081</v>
       </c>
       <c r="C45" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.01541875522536249</v>
+        <v>-0.4809077360151081</v>
       </c>
       <c r="E45" t="n">
-        <v>0.707036489770475</v>
+        <v>-0.7207714474230212</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.07324087755738123</v>
+        <v>0.06980713814424469</v>
       </c>
       <c r="G45" t="n">
-        <v>46.33795612213094</v>
+        <v>53.49035690721223</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45199</v>
+        <v>40816</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1724705594338053</v>
+        <v>0.02244930521743372</v>
       </c>
       <c r="C46" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1724705594338053</v>
+        <v>-0.02244930521743372</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4458402383766479</v>
+        <v>0.03705704224126092</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.138539940405838</v>
+        <v>0.2592642605603152</v>
       </c>
       <c r="G46" t="n">
-        <v>43.0730029797081</v>
+        <v>62.96321302801577</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45230</v>
+        <v>40847</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.3465753426722331</v>
+        <v>0.2314217858449168</v>
       </c>
       <c r="C47" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3465753426722331</v>
+        <v>-0.2314217858449168</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6255706074934635</v>
+        <v>-0.007177448795898771</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.09360734812663413</v>
+        <v>0.2482056378010253</v>
       </c>
       <c r="G47" t="n">
-        <v>45.31963259366829</v>
+        <v>62.41028189005127</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45260</v>
+        <v>40877</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.1558852172542286</v>
+        <v>0.1121931842406315</v>
       </c>
       <c r="C48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1558852172542286</v>
+        <v>-0.1121931842406315</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7437047370328701</v>
+        <v>0.05979279470312476</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.06407381574178247</v>
+        <v>0.2649481986757812</v>
       </c>
       <c r="G48" t="n">
-        <v>46.79630921291088</v>
+        <v>63.24740993378906</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45291</v>
+        <v>40908</v>
       </c>
       <c r="B49" t="n">
-        <v>0.4842793693184613</v>
+        <v>-0.006619404085575804</v>
       </c>
       <c r="C49" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4842793693184613</v>
+        <v>0.006619404085575804</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7219974850701719</v>
+        <v>0.3385776606240166</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.06950062873245702</v>
+        <v>0.3346444151560041</v>
       </c>
       <c r="G49" t="n">
-        <v>46.52496856337715</v>
+        <v>66.73222075780021</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45322</v>
+        <v>40939</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1900410772115576</v>
+        <v>0.05821659155618468</v>
       </c>
       <c r="C50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1900410772115576</v>
+        <v>-0.05821659155618468</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7259892961457124</v>
+        <v>0.3398193647634125</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0685026759635719</v>
+        <v>0.3349548411908531</v>
       </c>
       <c r="G50" t="n">
-        <v>46.57486620182141</v>
+        <v>66.74774205954266</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45351</v>
+        <v>40968</v>
       </c>
       <c r="B51" t="n">
-        <v>0.725101488334623</v>
+        <v>0.2144654955349065</v>
       </c>
       <c r="C51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.725101488334623</v>
+        <v>-0.2144654955349065</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6720394917348356</v>
+        <v>0.3371208523143348</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.08199012706629111</v>
+        <v>0.3342802130785837</v>
       </c>
       <c r="G51" t="n">
-        <v>45.90049364668545</v>
+        <v>66.71401065392919</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45382</v>
+        <v>40999</v>
       </c>
       <c r="B52" t="n">
-        <v>0.7968935870705939</v>
+        <v>0.2649576656510516</v>
       </c>
       <c r="C52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7968935870705939</v>
+        <v>-0.2649576656510516</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3961558269983183</v>
+        <v>0.4287612049211006</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1509610432504204</v>
+        <v>0.3571903012302752</v>
       </c>
       <c r="G52" t="n">
-        <v>42.45194783747898</v>
+        <v>67.85951506151375</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45412</v>
+        <v>41029</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2558601105346199</v>
+        <v>0.1375421663201841</v>
       </c>
       <c r="C53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2558601105346199</v>
+        <v>-0.1375421663201841</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3357134767270401</v>
+        <v>0.5433350435510442</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.16607163081824</v>
+        <v>0.3858337608877611</v>
       </c>
       <c r="G53" t="n">
-        <v>41.696418459088</v>
+        <v>69.29168804438805</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45443</v>
+        <v>41060</v>
       </c>
       <c r="B54" t="n">
-        <v>0.4859216269890231</v>
+        <v>0.01919667063693074</v>
       </c>
       <c r="C54" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4859216269890231</v>
+        <v>-0.01919667063693074</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1884040167158942</v>
+        <v>0.7333284836962094</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2028989958210264</v>
+        <v>0.4333321209240523</v>
       </c>
       <c r="G54" t="n">
-        <v>39.85505020894868</v>
+        <v>71.66660604620262</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45473</v>
+        <v>41090</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4303453592154325</v>
+        <v>0.09664727497593595</v>
       </c>
       <c r="C55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4303453592154325</v>
+        <v>-0.09664727497593595</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2102251105290874</v>
+        <v>0.5624946387506086</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1974437223677281</v>
+        <v>0.3906236596876521</v>
       </c>
       <c r="G55" t="n">
-        <v>40.12781388161359</v>
+        <v>69.53118298438261</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45504</v>
+        <v>41121</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2246016013212657</v>
+        <v>0.4331181389168922</v>
       </c>
       <c r="C56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2246016013212657</v>
+        <v>-0.4331181389168922</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6271468092454271</v>
+        <v>0.5171481426717255</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.09321329768864323</v>
+        <v>0.3792870356679314</v>
       </c>
       <c r="G56" t="n">
-        <v>45.33933511556783</v>
+        <v>68.96435178339657</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45535</v>
+        <v>41152</v>
       </c>
       <c r="B57" t="n">
-        <v>0.4793566694161478</v>
+        <v>0.8482802023764155</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4793566694161478</v>
+        <v>-0.8482802023764155</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6966460935674826</v>
+        <v>0.296171470325545</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4241615233918706</v>
+        <v>0.3240428675813862</v>
       </c>
       <c r="G57" t="n">
-        <v>71.20807616959353</v>
+        <v>66.20214337906931</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45565</v>
+        <v>41182</v>
       </c>
       <c r="B58" t="n">
-        <v>0.9887062872289741</v>
+        <v>1</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.9887062872289741</v>
+        <v>-1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7135818193454528</v>
+        <v>-0.18727750114294</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4283954548363632</v>
+        <v>0.203180624714265</v>
       </c>
       <c r="G58" t="n">
-        <v>71.41977274181816</v>
+        <v>60.15903123571324</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45596</v>
+        <v>41213</v>
       </c>
       <c r="B59" t="n">
-        <v>0.9939904295098646</v>
+        <v>0.5084720169303274</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.9939904295098646</v>
+        <v>-0.5084720169303274</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5983624558508628</v>
+        <v>0.2077543381878241</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3995906139627157</v>
+        <v>0.301938584546956</v>
       </c>
       <c r="G59" t="n">
-        <v>69.97953069813579</v>
+        <v>65.0969292273478</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45626</v>
+        <v>41243</v>
       </c>
       <c r="B60" t="n">
-        <v>0.8366865798593541</v>
+        <v>0.5507560330874943</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8366865798593541</v>
+        <v>-0.5507560330874943</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5692794149905193</v>
+        <v>0.1315365655946139</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3923198537476298</v>
+        <v>0.2828841413986535</v>
       </c>
       <c r="G60" t="n">
-        <v>69.61599268738149</v>
+        <v>64.14420706993266</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45657</v>
+        <v>41274</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3602942702329341</v>
+        <v>0.5126546404279868</v>
       </c>
       <c r="C61" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.3602942702329341</v>
+        <v>-0.5126546404279868</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3481680958229711</v>
+        <v>0.07406331235127452</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1629579760442572</v>
+        <v>0.2685158280878187</v>
       </c>
       <c r="G61" t="n">
-        <v>41.85210119778714</v>
+        <v>63.42579140439093</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45688</v>
+        <v>41305</v>
       </c>
       <c r="B62" t="n">
-        <v>0.3975229153322723</v>
+        <v>0.5521878136034833</v>
       </c>
       <c r="C62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.3975229153322723</v>
+        <v>-0.5521878136034833</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3223175793058123</v>
+        <v>0.1088403659500817</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1694206051735469</v>
+        <v>0.2772100914875204</v>
       </c>
       <c r="G62" t="n">
-        <v>41.52896974132265</v>
+        <v>63.86050457437602</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45716</v>
+        <v>41333</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.02539808776075768</v>
+        <v>0.3832100837766666</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02539808776075768</v>
+        <v>-0.3832100837766666</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2599884586309352</v>
+        <v>0.452180024715489</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3149971146577338</v>
+        <v>0.3630450061788723</v>
       </c>
       <c r="G63" t="n">
-        <v>65.7498557328867</v>
+        <v>68.15225030894361</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45747</v>
+        <v>41364</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.631201657753489</v>
+        <v>0.4129727475015758</v>
       </c>
       <c r="C64" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0.631201657753489</v>
+        <v>-0.4129727475015758</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3347664390411321</v>
+        <v>0.3974415448310449</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1663083902397169</v>
+        <v>0.3493603862077612</v>
       </c>
       <c r="G64" t="n">
-        <v>41.68458048801416</v>
+        <v>67.46801931038806</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45777</v>
+        <v>41394</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.5142851840573717</v>
+        <v>0.5303798613344407</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5142851840573717</v>
+        <v>-0.5303798613344407</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7657487200526374</v>
+        <v>0.4224135219214957</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4414371800131593</v>
+        <v>0.3556033804803739</v>
       </c>
       <c r="G65" t="n">
-        <v>72.07185900065797</v>
+        <v>67.78016902401869</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45808</v>
+        <v>41425</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.3087200316538415</v>
+        <v>0.9777398588571673</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3087200316538415</v>
+        <v>-0.9777398588571673</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7115601527834433</v>
+        <v>0.1149512223896378</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4278900381958608</v>
+        <v>-0.2212621944025905</v>
       </c>
       <c r="G66" t="n">
-        <v>71.39450190979304</v>
+        <v>38.93689027987048</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45838</v>
+        <v>41455</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.2402751689772532</v>
+        <v>0.8050359477128936</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2402751689772532</v>
+        <v>-0.8050359477128936</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4897783252385236</v>
+        <v>0.1437972934724853</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3724445813096309</v>
+        <v>-0.2140506766318787</v>
       </c>
       <c r="G67" t="n">
-        <v>68.62222906548155</v>
+        <v>39.29746616840607</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45869</v>
+        <v>41486</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.01852746185086141</v>
+        <v>0.8478876696228324</v>
       </c>
       <c r="C68" t="n">
         <v>-1</v>
       </c>
       <c r="D68" t="n">
-        <v>0.01852746185086141</v>
+        <v>-0.8478876696228324</v>
       </c>
       <c r="E68" t="n">
-        <v>0.1541823954041822</v>
+        <v>0.3790725812026023</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.2114544011489544</v>
+        <v>-0.1552318546993494</v>
       </c>
       <c r="G68" t="n">
-        <v>39.42727994255228</v>
+        <v>42.23840726503253</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45900</v>
+        <v>41517</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.08049051226856291</v>
+        <v>0.5689765567494039</v>
       </c>
       <c r="C69" t="n">
         <v>-1</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08049051226856291</v>
+        <v>-0.5689765567494039</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2044195473011145</v>
+        <v>0.3880070767070931</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.1988951131747214</v>
+        <v>-0.1529982308232267</v>
       </c>
       <c r="G69" t="n">
-        <v>40.05524434126393</v>
+        <v>42.35008845883866</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45930</v>
+        <v>41547</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.01010868639871142</v>
+        <v>0.5853998713206033</v>
       </c>
       <c r="C70" t="n">
         <v>-1</v>
       </c>
       <c r="D70" t="n">
-        <v>0.01010868639871142</v>
+        <v>-0.5853998713206033</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1829447638305253</v>
+        <v>0.5033760288156808</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.2042638090423687</v>
+        <v>-0.1241559927960798</v>
       </c>
       <c r="G70" t="n">
-        <v>39.78680954788156</v>
+        <v>43.79220036019601</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45961</v>
+        <v>41578</v>
       </c>
       <c r="B71" t="n">
-        <v>0.05502556617613721</v>
+        <v>0.8892544436685994</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.05502556617613721</v>
+        <v>-0.8892544436685994</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1396958306639401</v>
+        <v>0.3943574725576549</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2849239576659851</v>
+        <v>-0.1514106318605863</v>
       </c>
       <c r="G71" t="n">
-        <v>64.24619788329925</v>
+        <v>42.42946840697068</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45991</v>
+        <v>41608</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.1793780480903746</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1793780480903746</v>
+        <v>-1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.06727329548446213</v>
+        <v>0.4807703653326779</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2668183238711155</v>
+        <v>-0.1298074086668305</v>
       </c>
       <c r="G72" t="n">
-        <v>63.34091619355577</v>
+        <v>43.50962956665848</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46022</v>
+        <v>41639</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.03985616928748816</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D73" t="n">
-        <v>0.03985616928748816</v>
+        <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.08895036738486296</v>
+        <v>0.4310499065910437</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2722375918462158</v>
+        <v>-0.1422375233522391</v>
       </c>
       <c r="G73" t="n">
-        <v>63.61187959231079</v>
+        <v>42.88812383238805</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46053</v>
+        <v>41670</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.1350939033184604</v>
+        <v>0.6010310089526316</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1350939033184604</v>
+        <v>-0.6010310089526316</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1533855298950429</v>
+        <v>0.6096780598761148</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2116536175262393</v>
+        <v>-0.0975804850309713</v>
       </c>
       <c r="G74" t="n">
-        <v>60.58268087631197</v>
+        <v>45.12097574845144</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46081</v>
+        <v>41698</v>
       </c>
       <c r="B75" t="n">
-        <v>0.05317514695989068</v>
+        <v>0.8039201044290348</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.05317514695989068</v>
+        <v>-0.8039201044290348</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.2444017704789831</v>
+        <v>0.2390862615853299</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1888995573802542</v>
+        <v>-0.1902284346036675</v>
       </c>
       <c r="G75" t="n">
-        <v>59.4449778690127</v>
+        <v>40.48857826981662</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46112</v>
+        <v>41729</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.008717140558185191</v>
+        <v>0.6506351167104657</v>
       </c>
       <c r="C76" t="n">
         <v>-1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.008717140558185191</v>
+        <v>-0.6506351167104657</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.8873902561975565</v>
+        <v>0.2704011193828281</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.4718475640493891</v>
+        <v>-0.182399720154293</v>
       </c>
       <c r="G76" t="n">
-        <v>26.40762179753055</v>
+        <v>40.88001399228535</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
+        <v>41759</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.6306202238900704</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.6306202238900704</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.03553965171684869</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-0.2411150870707878</v>
+      </c>
+      <c r="G77" t="n">
+        <v>37.94424564646061</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>41790</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.576124597079269</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-0.576124597079269</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.09921116201034121</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.2748027905025853</v>
+      </c>
+      <c r="G78" t="n">
+        <v>63.74013952512927</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>41820</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.7244486680774359</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-0.7244486680774359</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.06887402637624647</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.2327814934059383</v>
+      </c>
+      <c r="G79" t="n">
+        <v>61.63907467029692</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>41851</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.3438606218425948</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.3438606218425948</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.2228086629152292</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.3057021657288073</v>
+      </c>
+      <c r="G80" t="n">
+        <v>65.28510828644036</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>41882</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.7778599074131626</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.7778599074131626</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3562861639538759</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.339071540988469</v>
+      </c>
+      <c r="G81" t="n">
+        <v>66.95357704942346</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>41912</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.4784303309638653</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-0.4784303309638653</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.474577691265854</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.3686444228164635</v>
+      </c>
+      <c r="G82" t="n">
+        <v>68.43222114082317</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>41943</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.3855728822060733</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-0.3855728822060733</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.5854759645601858</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.3963689911400464</v>
+      </c>
+      <c r="G83" t="n">
+        <v>69.81844955700231</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>41973</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.3832526716545966</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.3832526716545966</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.8797669922189842</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.4699417480547461</v>
+      </c>
+      <c r="G84" t="n">
+        <v>73.49708740273731</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>42004</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.2832485997311141</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-0.2832485997311141</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>42035</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.2621783559741739</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-0.2621783559741739</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>42063</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.3156800617781103</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-0.3156800617781103</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>42094</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.1497245861169263</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-0.1497245861169263</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G88" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>42124</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.1982310032552878</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-0.1982310032552878</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>42155</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.1456765434550095</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-0.1456765434550095</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>42185</v>
+      </c>
+      <c r="B91" t="n">
+        <v>-0.1022739504078421</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.1022739504078421</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>42216</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.1349787712166808</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-0.1349787712166808</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>42247</v>
+      </c>
+      <c r="B93" t="n">
+        <v>-0.3973745023361989</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.3973745023361989</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>42277</v>
+      </c>
+      <c r="B94" t="n">
+        <v>-0.3858157778024258</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.3858157778024258</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>42308</v>
+      </c>
+      <c r="B95" t="n">
+        <v>-0.1599154073700874</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.1599154073700874</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G95" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>42338</v>
+      </c>
+      <c r="B96" t="n">
+        <v>-0.2451150258192877</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.2451150258192877</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>42369</v>
+      </c>
+      <c r="B97" t="n">
+        <v>-0.3509296869371307</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.3509296869371307</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9270649622122249</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.4817662405530562</v>
+      </c>
+      <c r="G97" t="n">
+        <v>74.08831202765282</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>42400</v>
+      </c>
+      <c r="B98" t="n">
+        <v>-0.4563052266035448</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.4563052266035448</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9120550299623522</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.4780137574905881</v>
+      </c>
+      <c r="G98" t="n">
+        <v>73.9006878745294</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>42429</v>
+      </c>
+      <c r="B99" t="n">
+        <v>-0.7488359199607031</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.7488359199607031</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9880362912496399</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.49700907281241</v>
+      </c>
+      <c r="G99" t="n">
+        <v>74.8504536406205</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>42460</v>
+      </c>
+      <c r="B100" t="n">
+        <v>-0.3039306209582812</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.3039306209582812</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.7805431034231494</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.4451357758557873</v>
+      </c>
+      <c r="G100" t="n">
+        <v>72.25678879278937</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>42490</v>
+      </c>
+      <c r="B101" t="n">
+        <v>-0.4061223116754205</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.4061223116754205</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6491000144837743</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.4122750036209436</v>
+      </c>
+      <c r="G101" t="n">
+        <v>70.61375018104718</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>42521</v>
+      </c>
+      <c r="B102" t="n">
+        <v>-0.3327254485320612</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.3327254485320612</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.5516670920669302</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.3879167730167326</v>
+      </c>
+      <c r="G102" t="n">
+        <v>69.39583865083662</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>42551</v>
+      </c>
+      <c r="B103" t="n">
+        <v>-0.2382511138901809</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.2382511138901809</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.3892459125115739</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.3473114781278935</v>
+      </c>
+      <c r="G103" t="n">
+        <v>67.36557390639467</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>42582</v>
+      </c>
+      <c r="B104" t="n">
+        <v>-0.1306900314939579</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.1306900314939579</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.2239133419362755</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.3059783354840689</v>
+      </c>
+      <c r="G104" t="n">
+        <v>65.29891677420345</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>42613</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.289756352527264</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-0.289756352527264</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.09820581798704786</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.274551454496762</v>
+      </c>
+      <c r="G105" t="n">
+        <v>63.7275727248381</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>42643</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.2695207876063175</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-0.2695207876063175</v>
+      </c>
+      <c r="E106" t="n">
+        <v>-0.09455486084681654</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.2263612847882959</v>
+      </c>
+      <c r="G106" t="n">
+        <v>61.3180642394148</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>42674</v>
+      </c>
+      <c r="B107" t="n">
+        <v>-0.2543678616607846</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.2543678616607846</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-0.08894599685950282</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.2277635007851243</v>
+      </c>
+      <c r="G107" t="n">
+        <v>61.38817503925622</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>42704</v>
+      </c>
+      <c r="B108" t="n">
+        <v>-0.005430526108636872</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.005430526108636872</v>
+      </c>
+      <c r="E108" t="n">
+        <v>-0.4484666800765899</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.1378833299808525</v>
+      </c>
+      <c r="G108" t="n">
+        <v>56.89416649904263</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>42735</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.2863297592161509</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-0.2863297592161509</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-0.8804424064865564</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.02988939837836091</v>
+      </c>
+      <c r="G109" t="n">
+        <v>51.49446991891804</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>42766</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.7299763297910437</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-0.7299763297910437</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>42794</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.7089283833925143</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-0.7089283833925143</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>42825</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.4292660302510641</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-0.4292660302510641</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-0.798426359472987</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-0.4496065898682468</v>
+      </c>
+      <c r="G112" t="n">
+        <v>27.51967050658766</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>42855</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.4837133782267932</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-0.4837133782267932</v>
+      </c>
+      <c r="E113" t="n">
+        <v>-0.148864977984589</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-0.2872162444961472</v>
+      </c>
+      <c r="G113" t="n">
+        <v>35.63918777519264</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>42886</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.449803090430026</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-0.449803090430026</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-0.01850437300627004</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-0.2546260932515675</v>
+      </c>
+      <c r="G114" t="n">
+        <v>37.26869533742163</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>42916</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.4606366591054505</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-0.4606366591054505</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.1851429759208702</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-0.2037142560197824</v>
+      </c>
+      <c r="G115" t="n">
+        <v>39.81428719901088</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>42947</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.3773790272101165</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-0.3773790272101165</v>
+      </c>
+      <c r="E116" t="n">
+        <v>-0.3747866903144558</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-0.343696672578614</v>
+      </c>
+      <c r="G116" t="n">
+        <v>32.8151663710693</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>42978</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3757405753396203</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-0.3757405753396203</v>
+      </c>
+      <c r="E117" t="n">
+        <v>-0.3300953977070161</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-0.3325238494267541</v>
+      </c>
+      <c r="G117" t="n">
+        <v>33.3738075286623</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>43008</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.4963141991149894</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-0.4963141991149894</v>
+      </c>
+      <c r="E118" t="n">
+        <v>-0.1891676950891684</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-0.2972919237722921</v>
+      </c>
+      <c r="G118" t="n">
+        <v>35.13540381138539</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>43039</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.8030326226014249</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-0.8030326226014249</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.3444563264339708</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.3361140816084927</v>
+      </c>
+      <c r="G119" t="n">
+        <v>33.19429591957537</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>43069</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.7313368478898306</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-0.7313368478898306</v>
+      </c>
+      <c r="E120" t="n">
+        <v>-0.2551295275381696</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.1862176181154576</v>
+      </c>
+      <c r="G120" t="n">
+        <v>59.31088090577288</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>43100</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.6439715906334685</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-0.6439715906334685</v>
+      </c>
+      <c r="E121" t="n">
+        <v>-0.2754861252932329</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.1811284686766917</v>
+      </c>
+      <c r="G121" t="n">
+        <v>59.0564234338346</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>43131</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.8814558255022933</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.8814558255022933</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.3769929724113797</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-0.344248243102845</v>
+      </c>
+      <c r="G122" t="n">
+        <v>32.78758784485775</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>43159</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.2884960077153638</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-0.2884960077153638</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-0.282979511983014</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-0.3207448779957535</v>
+      </c>
+      <c r="G123" t="n">
+        <v>33.96275610021232</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>43190</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.1738277860966868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-0.1738277860966868</v>
+      </c>
+      <c r="E124" t="n">
+        <v>-0.554701378088747</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-0.3886753445221868</v>
+      </c>
+      <c r="G124" t="n">
+        <v>30.56623277389066</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>43220</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.1395897887385053</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-0.1395897887385053</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.8183142394135237</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-0.4545785598533809</v>
+      </c>
+      <c r="G125" t="n">
+        <v>27.27107200733095</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>43251</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.1624933753740008</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.1624933753740008</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>43281</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.2028979973742805</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-0.2028979973742805</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.9646368427506588</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.4911592106876647</v>
+      </c>
+      <c r="G127" t="n">
+        <v>25.44203946561677</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>43312</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.2852715698037918</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-0.2852715698037918</v>
+      </c>
+      <c r="E128" t="n">
+        <v>-0.6986842355294195</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-0.4246710588823549</v>
+      </c>
+      <c r="G128" t="n">
+        <v>28.76644705588226</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>43343</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.4714244996433808</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-0.4714244996433808</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-0.651403415880294</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-0.4128508539700735</v>
+      </c>
+      <c r="G129" t="n">
+        <v>29.35745730149632</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>43373</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3818410296702609</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.3818410296702609</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.7190357031293871</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-0.4297589257823468</v>
+      </c>
+      <c r="G130" t="n">
+        <v>28.51205371088266</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>43404</v>
+      </c>
+      <c r="B131" t="n">
+        <v>-0.2278167133284522</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.2278167133284522</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-0.2712440722634438</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-0.3178110180658609</v>
+      </c>
+      <c r="G131" t="n">
+        <v>34.10944909670695</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>43434</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-0.2842792650042066</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.2842792650042066</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.2262043505531956</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-0.1934489123617011</v>
+      </c>
+      <c r="G132" t="n">
+        <v>40.32755438191494</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>43465</v>
+      </c>
+      <c r="B133" t="n">
+        <v>-0.891037883042496</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.891037883042496</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4496856237495168</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-0.1375785940626208</v>
+      </c>
+      <c r="G133" t="n">
+        <v>43.12107029686896</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>43496</v>
+      </c>
+      <c r="B134" t="n">
+        <v>-0.7668713647823872</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.7668713647823872</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.2998045884951204</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.3249511471237801</v>
+      </c>
+      <c r="G134" t="n">
+        <v>66.24755735618901</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>43524</v>
+      </c>
+      <c r="B135" t="n">
+        <v>-0.3757333759844713</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3757333759844713</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.071885606044002</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.2679714015110005</v>
+      </c>
+      <c r="G135" t="n">
+        <v>63.39857007555003</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>43555</v>
+      </c>
+      <c r="B136" t="n">
+        <v>-0.1002086025112549</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.1002086025112549</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.1774820284190736</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2943705071047684</v>
+      </c>
+      <c r="G136" t="n">
+        <v>64.71852535523843</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>43585</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.1154520186943851</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.1154520186943851</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2620990024639672</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3155247506159918</v>
+      </c>
+      <c r="G137" t="n">
+        <v>65.77623753079959</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>43616</v>
+      </c>
+      <c r="B138" t="n">
+        <v>-0.4434939501167779</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4434939501167779</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5893554189822291</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3973388547455573</v>
+      </c>
+      <c r="G138" t="n">
+        <v>69.86694273727787</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>43646</v>
+      </c>
+      <c r="B139" t="n">
+        <v>-0.06013669600888082</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.06013669600888082</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3273696359598009</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3318424089899502</v>
+      </c>
+      <c r="G139" t="n">
+        <v>66.59212044949751</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>43677</v>
+      </c>
+      <c r="B140" t="n">
+        <v>-0.2036829459521066</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.2036829459521066</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3193690578101936</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3298422644525484</v>
+      </c>
+      <c r="G140" t="n">
+        <v>66.49211322262742</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>43708</v>
+      </c>
+      <c r="B141" t="n">
+        <v>-0.4952697290291083</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.4952697290291083</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.5207509170069858</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3801877292517465</v>
+      </c>
+      <c r="G141" t="n">
+        <v>69.00938646258732</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>43738</v>
+      </c>
+      <c r="B142" t="n">
+        <v>-0.4155169773521743</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4155169773521743</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5929388656187067</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.3982347164046767</v>
+      </c>
+      <c r="G142" t="n">
+        <v>69.91173582023383</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>43769</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.1772755197176602</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-0.1772755197176602</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3011990650025461</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3252997662506365</v>
+      </c>
+      <c r="G143" t="n">
+        <v>66.26498831253183</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>43799</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.3368026835401541</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-0.3368026835401541</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-0.101993221539738</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.2245016946150655</v>
+      </c>
+      <c r="G144" t="n">
+        <v>61.22508473075327</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>43830</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-0.5546813032312741</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.1113296741921815</v>
+      </c>
+      <c r="G145" t="n">
+        <v>55.56648370960907</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>43861</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.5909266081672554</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-0.5909266081672554</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.1760555858030105</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.2940138964507526</v>
+      </c>
+      <c r="G146" t="n">
+        <v>64.70069482253763</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>43890</v>
+      </c>
+      <c r="B147" t="n">
+        <v>-0.2094496202401305</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.2094496202401305</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.4759182924188182</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.3689795731047045</v>
+      </c>
+      <c r="G147" t="n">
+        <v>68.44897865523522</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>43921</v>
+      </c>
+      <c r="B148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>43951</v>
+      </c>
+      <c r="B149" t="n">
+        <v>-0.5316951219698263</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.5316951219698263</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G149" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>43982</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.1292260049356416</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-0.1292260049356416</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.82362361887463</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0.4559059047186574</v>
+      </c>
+      <c r="G150" t="n">
+        <v>72.79529523593287</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>44012</v>
+      </c>
+      <c r="B151" t="n">
+        <v>-0.2549242486435401</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.2549242486435401</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.7415268894781476</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0.4353817223695369</v>
+      </c>
+      <c r="G151" t="n">
+        <v>71.76908611847685</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>44043</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.2125924859070487</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-0.2125924859070487</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.4809809859984314</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0.3702452464996078</v>
+      </c>
+      <c r="G152" t="n">
+        <v>68.51226232498038</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>44074</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.7385660294031787</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-0.7385660294031787</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.200342178510152</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.300085544627538</v>
+      </c>
+      <c r="G153" t="n">
+        <v>65.00427723137689</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>44104</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.5048067465123661</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-0.5048067465123661</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.3828248090282613</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0.3457062022570653</v>
+      </c>
+      <c r="G154" t="n">
+        <v>67.28531011285325</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>44135</v>
+      </c>
+      <c r="B155" t="n">
+        <v>-0.06969639647952014</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.06969639647952014</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.6744123433317434</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0.4186030858329358</v>
+      </c>
+      <c r="G155" t="n">
+        <v>70.9301542916468</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>44165</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.5168871523547388</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-0.5168871523547388</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.2214647783204046</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.3053661945801011</v>
+      </c>
+      <c r="G156" t="n">
+        <v>65.26830972900505</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>44196</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.5050457970259344</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-0.5050457970259344</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.293720323694956</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0.323430080923739</v>
+      </c>
+      <c r="G157" t="n">
+        <v>66.17150404618695</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>44227</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.4508700930528733</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-0.4508700930528733</v>
+      </c>
+      <c r="E158" t="n">
+        <v>-0.2882861612047909</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.1779284596988023</v>
+      </c>
+      <c r="G158" t="n">
+        <v>58.89642298494011</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>44255</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G159" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>44286</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G160" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>44316</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G161" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>44347</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G162" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>44377</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G163" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>44408</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G164" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>44439</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G165" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>44469</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G166" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>44500</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G167" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>44530</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.8511426119261823</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-0.8511426119261823</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G168" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G169" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.4618565981996479</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-0.4618565981996479</v>
+      </c>
+      <c r="E170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G170" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.1780681941987146</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-0.1780681941987146</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G171" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.07001597416442971</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-0.07001597416442971</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G172" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>44681</v>
+      </c>
+      <c r="B173" t="n">
+        <v>-0.6536862725519565</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.6536862725519565</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G173" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="B174" t="n">
+        <v>-0.669981711867113</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.669981711867113</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G174" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G175" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>44773</v>
+      </c>
+      <c r="B176" t="n">
+        <v>-0.9067331770288718</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.9067331770288718</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G176" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>44804</v>
+      </c>
+      <c r="B177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G177" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-0.5179999986345991</v>
+      </c>
+      <c r="F178" t="n">
+        <v>-0.3794999996586498</v>
+      </c>
+      <c r="G178" t="n">
+        <v>31.02500001706751</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>44865</v>
+      </c>
+      <c r="B179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>-0.511036083715925</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-0.3777590209289813</v>
+      </c>
+      <c r="G179" t="n">
+        <v>31.11204895355094</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>44895</v>
+      </c>
+      <c r="B180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G180" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-0.5989552243790301</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-0.3997388060947575</v>
+      </c>
+      <c r="G181" t="n">
+        <v>30.01305969526212</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>-0.3055267476541731</v>
+      </c>
+      <c r="F182" t="n">
+        <v>-0.3263816869135433</v>
+      </c>
+      <c r="G182" t="n">
+        <v>33.68091565432284</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>44985</v>
+      </c>
+      <c r="B183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.1273672996050453</v>
+      </c>
+      <c r="F183" t="n">
+        <v>-0.2181581750987387</v>
+      </c>
+      <c r="G183" t="n">
+        <v>39.09209124506307</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.448084492021296</v>
+      </c>
+      <c r="F184" t="n">
+        <v>-0.137978876994676</v>
+      </c>
+      <c r="G184" t="n">
+        <v>43.1010561502662</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>45046</v>
+      </c>
+      <c r="B185" t="n">
+        <v>-0.7751571022816153</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.7751571022816153</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.6816524879075884</v>
+      </c>
+      <c r="F185" t="n">
+        <v>-0.07958687802310291</v>
+      </c>
+      <c r="G185" t="n">
+        <v>46.02065609884485</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>45077</v>
+      </c>
+      <c r="B186" t="n">
+        <v>-0.5674423617276769</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.5674423617276769</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.9984256691439025</v>
+      </c>
+      <c r="F186" t="n">
+        <v>-0.0003935827140243708</v>
+      </c>
+      <c r="G186" t="n">
+        <v>49.98032086429878</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B187" t="n">
+        <v>0.3357862111056159</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-0.3357862111056159</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0.6629255378352946</v>
+      </c>
+      <c r="F187" t="n">
+        <v>-0.08426861554117634</v>
+      </c>
+      <c r="G187" t="n">
+        <v>45.78656922294118</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>45138</v>
+      </c>
+      <c r="B188" t="n">
+        <v>-0.04924585882379926</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.04924585882379926</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.3043036699719792</v>
+      </c>
+      <c r="F188" t="n">
+        <v>-0.1739240825070052</v>
+      </c>
+      <c r="G188" t="n">
+        <v>41.30379587464974</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B189" t="n">
+        <v>0.09564440856161512</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-0.09564440856161512</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0.2618957436422258</v>
+      </c>
+      <c r="F189" t="n">
+        <v>-0.1845260640894436</v>
+      </c>
+      <c r="G189" t="n">
+        <v>40.77369679552783</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B190" t="n">
+        <v>0.3018556115430632</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-0.3018556115430632</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-0.02668360823287819</v>
+      </c>
+      <c r="F190" t="n">
+        <v>-0.2566709020582195</v>
+      </c>
+      <c r="G190" t="n">
+        <v>37.16645489708903</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>45230</v>
+      </c>
+      <c r="B191" t="n">
+        <v>-0.2628824273689599</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.2628824273689599</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.1862858291997603</v>
+      </c>
+      <c r="F191" t="n">
+        <v>-0.2034285427000599</v>
+      </c>
+      <c r="G191" t="n">
+        <v>39.828572864997</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B192" t="n">
+        <v>-0.06022840437629199</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.06022840437629199</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.3313990058601781</v>
+      </c>
+      <c r="F192" t="n">
+        <v>-0.1671502485349555</v>
+      </c>
+      <c r="G192" t="n">
+        <v>41.64248757325223</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B193" t="n">
+        <v>0.6254878519153165</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>-0.6254878519153165</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.3195724087333729</v>
+      </c>
+      <c r="F193" t="n">
+        <v>-0.1701068978166568</v>
+      </c>
+      <c r="G193" t="n">
+        <v>41.49465510916716</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B194" t="n">
+        <v>0.3159024280025869</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D194" t="n">
+        <v>-0.3159024280025869</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0.3360623520522596</v>
+      </c>
+      <c r="F194" t="n">
+        <v>-0.1659844119869351</v>
+      </c>
+      <c r="G194" t="n">
+        <v>41.70077940065325</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="B195" t="n">
+        <v>0.8833758062416416</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D195" t="n">
+        <v>-0.8833758062416416</v>
+      </c>
+      <c r="E195" t="n">
+        <v>0.2866783237493731</v>
+      </c>
+      <c r="F195" t="n">
+        <v>-0.1783304190626567</v>
+      </c>
+      <c r="G195" t="n">
+        <v>41.08347904686717</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B196" t="n">
+        <v>0.9664521823444268</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D196" t="n">
+        <v>-0.9664521823444268</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-0.01467479819970579</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-0.2536686995499264</v>
+      </c>
+      <c r="G196" t="n">
+        <v>37.31656502250368</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>45412</v>
+      </c>
+      <c r="B197" t="n">
+        <v>0.4067944709292441</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>-0.4067944709292441</v>
+      </c>
+      <c r="E197" t="n">
+        <v>-0.0774881896174929</v>
+      </c>
+      <c r="F197" t="n">
+        <v>-0.2693720474043732</v>
+      </c>
+      <c r="G197" t="n">
+        <v>36.53139762978134</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>45443</v>
+      </c>
+      <c r="B198" t="n">
+        <v>0.6481180644128142</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D198" t="n">
+        <v>-0.6481180644128142</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-0.2376268903995719</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-0.309406722599893</v>
+      </c>
+      <c r="G198" t="n">
+        <v>34.52966387000535</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B199" t="n">
+        <v>0.5939538450247402</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>-0.5939538450247402</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-0.2108134965337405</v>
+      </c>
+      <c r="F199" t="n">
+        <v>-0.3027033741334351</v>
+      </c>
+      <c r="G199" t="n">
+        <v>34.86483129332824</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>45504</v>
+      </c>
+      <c r="B200" t="n">
+        <v>0.3847580886053642</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D200" t="n">
+        <v>-0.3847580886053642</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0.2506411827464734</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-0.1873397043133816</v>
+      </c>
+      <c r="G200" t="n">
+        <v>40.63301478433092</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>45535</v>
+      </c>
+      <c r="B201" t="n">
+        <v>0.6464727867105342</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>-0.6464727867105342</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.3348139324827769</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.3337034831206942</v>
+      </c>
+      <c r="G201" t="n">
+        <v>66.68517415603471</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0.3624294000466574</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0.3406073500116644</v>
+      </c>
+      <c r="G202" t="n">
+        <v>67.03036750058322</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>45596</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0.2459076157383074</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0.3114769039345768</v>
+      </c>
+      <c r="G203" t="n">
+        <v>65.57384519672884</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>45626</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0.2211881206557014</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0.3052970301639253</v>
+      </c>
+      <c r="G204" t="n">
+        <v>65.26485150819626</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0.5583156119856647</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>-0.5583156119856647</v>
+      </c>
+      <c r="E205" t="n">
+        <v>-0.0121356053184233</v>
+      </c>
+      <c r="F205" t="n">
+        <v>-0.2530339013296058</v>
+      </c>
+      <c r="G205" t="n">
+        <v>37.34830493351971</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.5973304527974895</v>
+      </c>
+      <c r="C206" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D206" t="n">
+        <v>-0.5973304527974895</v>
+      </c>
+      <c r="E206" t="n">
+        <v>-0.03650869140932936</v>
+      </c>
+      <c r="F206" t="n">
+        <v>-0.2591271728523323</v>
+      </c>
+      <c r="G206" t="n">
+        <v>37.04364135738339</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0.1757793731836468</v>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="n">
+        <v>-0.1757793731836468</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-0.100189169665097</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0.2249527075837257</v>
+      </c>
+      <c r="G207" t="n">
+        <v>61.24763537918628</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B208" t="n">
+        <v>-0.4276600415972277</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.4276600415972277</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-0.01778699403899107</v>
+      </c>
+      <c r="F208" t="n">
+        <v>-0.2544467485097477</v>
+      </c>
+      <c r="G208" t="n">
+        <v>37.27766257451262</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B209" t="n">
+        <v>-0.3173172953023464</v>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.3173172953023464</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0.4430628451366215</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0.3607657112841554</v>
+      </c>
+      <c r="G209" t="n">
+        <v>68.03828556420777</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B210" t="n">
+        <v>-0.1182432806334594</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.1182432806334594</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.3943181991226453</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.3485795497806613</v>
+      </c>
+      <c r="G210" t="n">
+        <v>67.42897748903307</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B211" t="n">
+        <v>-0.05314261934843294</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.05314261934843294</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.167144956621109</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.2917862391552772</v>
+      </c>
+      <c r="G211" t="n">
+        <v>64.58931195776387</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0.1622238966939956</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D212" t="n">
+        <v>-0.1622238966939956</v>
+      </c>
+      <c r="E212" t="n">
+        <v>-0.1824037269098642</v>
+      </c>
+      <c r="F212" t="n">
+        <v>-0.295600931727466</v>
+      </c>
+      <c r="G212" t="n">
+        <v>35.2199534136267</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0.1013469657401947</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>-0.1013469657401947</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-0.1280236292714688</v>
+      </c>
+      <c r="F213" t="n">
+        <v>-0.2820059073178672</v>
+      </c>
+      <c r="G213" t="n">
+        <v>35.89970463410664</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.1687321212079488</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>-0.1687321212079488</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-0.1485236996779091</v>
+      </c>
+      <c r="F214" t="n">
+        <v>-0.2871309249194773</v>
+      </c>
+      <c r="G214" t="n">
+        <v>35.64345375402613</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0.2310427309497884</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>-0.2310427309497884</v>
+      </c>
+      <c r="E215" t="n">
+        <v>-0.1917014210624619</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0.2020746447343845</v>
+      </c>
+      <c r="G215" t="n">
+        <v>60.10373223671923</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>45991</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0.005976803080494747</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>-0.005976803080494747</v>
+      </c>
+      <c r="E216" t="n">
+        <v>-0.2650874195298131</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0.1837281451175467</v>
+      </c>
+      <c r="G216" t="n">
+        <v>59.18640725587734</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0.1379640918599567</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>-0.1379640918599567</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-0.241641258455685</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0.1895896853860787</v>
+      </c>
+      <c r="G217" t="n">
+        <v>59.47948426930394</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0.04685666485050042</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>-0.04685666485050042</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-0.4885610964612435</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0.1278597258846891</v>
+      </c>
+      <c r="G218" t="n">
+        <v>56.39298629423446</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0.2239912666201547</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-0.2239912666201547</v>
+      </c>
+      <c r="E219" t="n">
+        <v>-0.5809804678694205</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0.1047548830326449</v>
+      </c>
+      <c r="G219" t="n">
+        <v>55.23774415163224</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B220" t="n">
+        <v>0.1654935631955197</v>
+      </c>
+      <c r="C220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-0.1654935631955197</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F220" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G220" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="B77" t="n">
-        <v>0.9135769709258238</v>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-0.9135769709258238</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>-2.775557561562891e-17</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
         <v>50</v>
       </c>
     </row>

--- a/ptr_position.xlsx
+++ b/ptr_position.xlsx
@@ -1161,13 +1161,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09636835888532423</v>
+        <v>0.09636848240847364</v>
       </c>
       <c r="F32" t="n">
-        <v>0.274092089721331</v>
+        <v>0.2740921206021184</v>
       </c>
       <c r="G32" t="n">
-        <v>63.70460448606655</v>
+        <v>63.70460603010593</v>
       </c>
     </row>
     <row r="33">
@@ -1184,13 +1184,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.02685913742639891</v>
+        <v>0.02685927138440315</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2567147843565997</v>
+        <v>0.2567148178461008</v>
       </c>
       <c r="G33" t="n">
-        <v>62.83573921782999</v>
+        <v>62.83574089230504</v>
       </c>
     </row>
     <row r="34">
@@ -1207,13 +1207,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1844634646294006</v>
+        <v>-0.1844638628045426</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2038841338426499</v>
+        <v>0.2038840342988644</v>
       </c>
       <c r="G34" t="n">
-        <v>60.19420669213249</v>
+        <v>60.19420171494322</v>
       </c>
     </row>
     <row r="35">
@@ -1230,13 +1230,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.09478188099775604</v>
+        <v>-0.09478143852105796</v>
       </c>
       <c r="F35" t="n">
-        <v>0.226304529750561</v>
+        <v>0.2263046403697355</v>
       </c>
       <c r="G35" t="n">
-        <v>61.31522648752805</v>
+        <v>61.31523201848677</v>
       </c>
     </row>
     <row r="36">
@@ -1244,22 +1244,22 @@
         <v>40512</v>
       </c>
       <c r="B36" t="n">
-        <v>0.4523376763211556</v>
+        <v>0.4523338985541602</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4523376763211556</v>
+        <v>-0.4523338985541602</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06433217683865598</v>
+        <v>0.06433181171954405</v>
       </c>
       <c r="F36" t="n">
-        <v>0.266083044209664</v>
+        <v>0.266082952929886</v>
       </c>
       <c r="G36" t="n">
-        <v>63.3041522104832</v>
+        <v>63.3041476464943</v>
       </c>
     </row>
     <row r="37">
@@ -1267,22 +1267,22 @@
         <v>40543</v>
       </c>
       <c r="B37" t="n">
-        <v>0.6010085899255</v>
+        <v>0.601005542613388</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.6010085899255</v>
+        <v>-0.601005542613388</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.163089393680277</v>
+        <v>-0.1630894782613244</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2092276515799308</v>
+        <v>0.2092276304346689</v>
       </c>
       <c r="G37" t="n">
-        <v>60.46138257899653</v>
+        <v>60.46138152173345</v>
       </c>
     </row>
     <row r="38">
@@ -1290,22 +1290,22 @@
         <v>40574</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7871984460121464</v>
+        <v>0.7871992177129061</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.7871984460121464</v>
+        <v>-0.7871992177129061</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.4687098824166767</v>
+        <v>-0.4687087869586242</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1328225293958308</v>
+        <v>0.132822803260344</v>
       </c>
       <c r="G38" t="n">
-        <v>56.64112646979154</v>
+        <v>56.6411401630172</v>
       </c>
     </row>
     <row r="39">
@@ -1313,22 +1313,22 @@
         <v>40602</v>
       </c>
       <c r="B39" t="n">
-        <v>0.8426384288286446</v>
+        <v>0.8426401910209437</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8426384288286446</v>
+        <v>-0.8426401910209437</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6176036998743041</v>
+        <v>-0.6176034613852167</v>
       </c>
       <c r="F39" t="n">
-        <v>0.09559907503142398</v>
+        <v>0.09559913465369582</v>
       </c>
       <c r="G39" t="n">
-        <v>54.7799537515712</v>
+        <v>54.77995673268479</v>
       </c>
     </row>
     <row r="40">
@@ -1336,22 +1336,22 @@
         <v>40633</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5705924032910326</v>
+        <v>0.5705899907135251</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5705924032910326</v>
+        <v>-0.5705899907135251</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5930598441786412</v>
+        <v>-0.5930590870534925</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1017350389553397</v>
+        <v>0.1017352282366268</v>
       </c>
       <c r="G40" t="n">
-        <v>55.08675194776698</v>
+        <v>55.08676141183134</v>
       </c>
     </row>
     <row r="41">
@@ -1359,22 +1359,22 @@
         <v>40663</v>
       </c>
       <c r="B41" t="n">
-        <v>0.6227152803736784</v>
+        <v>0.6227155257786184</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.6227152803736784</v>
+        <v>-0.6227155257786184</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.7162154973329663</v>
+        <v>-0.7162150865930941</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07094612566675843</v>
+        <v>0.07094622835172645</v>
       </c>
       <c r="G41" t="n">
-        <v>53.54730628333792</v>
+        <v>53.54731141758632</v>
       </c>
     </row>
     <row r="42">
@@ -1382,22 +1382,22 @@
         <v>40694</v>
       </c>
       <c r="B42" t="n">
-        <v>0.9364610312111221</v>
+        <v>0.936457052597506</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.9364610312111221</v>
+        <v>-0.936457052597506</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.9576335175185765</v>
+        <v>-0.9576328537563132</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01059162062035587</v>
+        <v>0.01059178656092169</v>
       </c>
       <c r="G42" t="n">
-        <v>50.52958103101779</v>
+        <v>50.52958932804609</v>
       </c>
     </row>
     <row r="43">
@@ -1414,13 +1414,13 @@
         <v>-1</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.8748760156265414</v>
+        <v>-0.8748754969618904</v>
       </c>
       <c r="F43" t="n">
-        <v>0.03128099609336465</v>
+        <v>0.03128112575952741</v>
       </c>
       <c r="G43" t="n">
-        <v>51.56404980466823</v>
+        <v>51.56405628797637</v>
       </c>
     </row>
     <row r="44">
@@ -1428,22 +1428,22 @@
         <v>40755</v>
       </c>
       <c r="B44" t="n">
-        <v>0.6015587045419569</v>
+        <v>0.601558611175472</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6015587045419569</v>
+        <v>-0.601558611175472</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.6587910731314257</v>
+        <v>-0.6587911882498391</v>
       </c>
       <c r="F44" t="n">
-        <v>0.08530223171714357</v>
+        <v>0.08530220293754023</v>
       </c>
       <c r="G44" t="n">
-        <v>54.26511158585718</v>
+        <v>54.26511014687701</v>
       </c>
     </row>
     <row r="45">
@@ -1451,22 +1451,22 @@
         <v>40786</v>
       </c>
       <c r="B45" t="n">
-        <v>0.4809077360151081</v>
+        <v>0.480907059163355</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4809077360151081</v>
+        <v>-0.480907059163355</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.7207714474230212</v>
+        <v>-0.7207719399805882</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06980713814424469</v>
+        <v>0.06980701500485292</v>
       </c>
       <c r="G45" t="n">
-        <v>53.49035690721223</v>
+        <v>53.49035075024264</v>
       </c>
     </row>
     <row r="46">
@@ -1474,22 +1474,22 @@
         <v>40816</v>
       </c>
       <c r="B46" t="n">
-        <v>0.02244930521743372</v>
+        <v>0.02244893668259692</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.02244930521743372</v>
+        <v>-0.02244893668259692</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03705704224126092</v>
+        <v>0.03705743773821498</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2592642605603152</v>
+        <v>0.2592643594345537</v>
       </c>
       <c r="G46" t="n">
-        <v>62.96321302801577</v>
+        <v>62.96321797172768</v>
       </c>
     </row>
     <row r="47">
@@ -1497,22 +1497,22 @@
         <v>40847</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2314217858449168</v>
+        <v>0.2314272116978959</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2314217858449168</v>
+        <v>-0.2314272116978959</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.007177448795898771</v>
+        <v>-0.007177634609662534</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2482056378010253</v>
+        <v>0.2482055913475844</v>
       </c>
       <c r="G47" t="n">
-        <v>62.41028189005127</v>
+        <v>62.41027956737921</v>
       </c>
     </row>
     <row r="48">
@@ -1520,22 +1520,22 @@
         <v>40877</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1121931842406315</v>
+        <v>0.1121910789869999</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.1121931842406315</v>
+        <v>-0.1121910789869999</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05979279470312476</v>
+        <v>0.05979290609408552</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2649481986757812</v>
+        <v>0.2649482265235214</v>
       </c>
       <c r="G48" t="n">
-        <v>63.24740993378906</v>
+        <v>63.24741132617607</v>
       </c>
     </row>
     <row r="49">
@@ -1543,22 +1543,22 @@
         <v>40908</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.006619404085575804</v>
+        <v>-0.006613006471580886</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0.006619404085575804</v>
+        <v>0.006613006471580886</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3385776606240166</v>
+        <v>0.3385779661096438</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3346444151560041</v>
+        <v>0.3346444915274109</v>
       </c>
       <c r="G49" t="n">
-        <v>66.73222075780021</v>
+        <v>66.73222457637054</v>
       </c>
     </row>
     <row r="50">
@@ -1566,22 +1566,22 @@
         <v>40939</v>
       </c>
       <c r="B50" t="n">
-        <v>0.05821659155618468</v>
+        <v>0.0582177164593564</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.05821659155618468</v>
+        <v>-0.0582177164593564</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3398193647634125</v>
+        <v>0.3398189480111338</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3349548411908531</v>
+        <v>0.3349547370027834</v>
       </c>
       <c r="G50" t="n">
-        <v>66.74774205954266</v>
+        <v>66.74773685013918</v>
       </c>
     </row>
     <row r="51">
@@ -1589,22 +1589,22 @@
         <v>40968</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2144654955349065</v>
+        <v>0.2144683724226449</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2144654955349065</v>
+        <v>-0.2144683724226449</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3371208523143348</v>
+        <v>0.3371204579760398</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3342802130785837</v>
+        <v>0.33428011449401</v>
       </c>
       <c r="G51" t="n">
-        <v>66.71401065392919</v>
+        <v>66.7140057247005</v>
       </c>
     </row>
     <row r="52">
@@ -1612,22 +1612,22 @@
         <v>40999</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2649576656510516</v>
+        <v>0.2649544253605771</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2649576656510516</v>
+        <v>-0.2649544253605771</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4287612049211006</v>
+        <v>0.428761477680847</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3571903012302752</v>
+        <v>0.3571903694202118</v>
       </c>
       <c r="G52" t="n">
-        <v>67.85951506151375</v>
+        <v>67.85951847101059</v>
       </c>
     </row>
     <row r="53">
@@ -1635,22 +1635,22 @@
         <v>41029</v>
       </c>
       <c r="B53" t="n">
-        <v>0.1375421663201841</v>
+        <v>0.1375451326465816</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1375421663201841</v>
+        <v>-0.1375451326465816</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5433350435510442</v>
+        <v>0.5433355076419789</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3858337608877611</v>
+        <v>0.3858338769104948</v>
       </c>
       <c r="G53" t="n">
-        <v>69.29168804438805</v>
+        <v>69.29169384552473</v>
       </c>
     </row>
     <row r="54">
@@ -1658,22 +1658,22 @@
         <v>41060</v>
       </c>
       <c r="B54" t="n">
-        <v>0.01919667063693074</v>
+        <v>0.01920186240591649</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.01919667063693074</v>
+        <v>-0.01920186240591649</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7333284836962094</v>
+        <v>0.7333289190374355</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4333321209240523</v>
+        <v>0.4333322297593589</v>
       </c>
       <c r="G54" t="n">
-        <v>71.66660604620262</v>
+        <v>71.66661148796794</v>
       </c>
     </row>
     <row r="55">
@@ -1681,22 +1681,22 @@
         <v>41090</v>
       </c>
       <c r="B55" t="n">
-        <v>0.09664727497593595</v>
+        <v>0.09664578598224079</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.09664727497593595</v>
+        <v>-0.09664578598224079</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5624946387506086</v>
+        <v>0.5624944263740791</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3906236596876521</v>
+        <v>0.3906236065935197</v>
       </c>
       <c r="G55" t="n">
-        <v>69.53118298438261</v>
+        <v>69.53118032967599</v>
       </c>
     </row>
     <row r="56">
@@ -1704,22 +1704,22 @@
         <v>41121</v>
       </c>
       <c r="B56" t="n">
-        <v>0.4331181389168922</v>
+        <v>0.433118240759912</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4331181389168922</v>
+        <v>-0.433118240759912</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5171481426717255</v>
+        <v>0.5171483766958939</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3792870356679314</v>
+        <v>0.3792870941739734</v>
       </c>
       <c r="G56" t="n">
-        <v>68.96435178339657</v>
+        <v>68.96435470869868</v>
       </c>
     </row>
     <row r="57">
@@ -1727,22 +1727,22 @@
         <v>41152</v>
       </c>
       <c r="B57" t="n">
-        <v>0.8482802023764155</v>
+        <v>0.8482806682368472</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.8482802023764155</v>
+        <v>-0.8482806682368472</v>
       </c>
       <c r="E57" t="n">
-        <v>0.296171470325545</v>
+        <v>0.2961710321917082</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3240428675813862</v>
+        <v>0.324042758047927</v>
       </c>
       <c r="G57" t="n">
-        <v>66.20214337906931</v>
+        <v>66.20213790239634</v>
       </c>
     </row>
     <row r="58">
@@ -1759,13 +1759,13 @@
         <v>-1</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.18727750114294</v>
+        <v>-0.1872773823526492</v>
       </c>
       <c r="F58" t="n">
-        <v>0.203180624714265</v>
+        <v>0.2031806544118377</v>
       </c>
       <c r="G58" t="n">
-        <v>60.15903123571324</v>
+        <v>60.15903272059189</v>
       </c>
     </row>
     <row r="59">
@@ -1773,22 +1773,22 @@
         <v>41213</v>
       </c>
       <c r="B59" t="n">
-        <v>0.5084720169303274</v>
+        <v>0.5084673039939065</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5084720169303274</v>
+        <v>-0.5084673039939065</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2077543381878241</v>
+        <v>0.2077546694896784</v>
       </c>
       <c r="F59" t="n">
-        <v>0.301938584546956</v>
+        <v>0.3019386673724196</v>
       </c>
       <c r="G59" t="n">
-        <v>65.0969292273478</v>
+        <v>65.09693336862098</v>
       </c>
     </row>
     <row r="60">
@@ -1796,22 +1796,22 @@
         <v>41243</v>
       </c>
       <c r="B60" t="n">
-        <v>0.5507560330874943</v>
+        <v>0.5507565904655768</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5507560330874943</v>
+        <v>-0.5507565904655768</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1315365655946139</v>
+        <v>0.1315369093165429</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2828841413986535</v>
+        <v>0.2828842273291357</v>
       </c>
       <c r="G60" t="n">
-        <v>64.14420706993266</v>
+        <v>64.14421136645679</v>
       </c>
     </row>
     <row r="61">
@@ -1819,22 +1819,22 @@
         <v>41274</v>
       </c>
       <c r="B61" t="n">
-        <v>0.5126546404279868</v>
+        <v>0.512651584448034</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5126546404279868</v>
+        <v>-0.512651584448034</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07406331235127452</v>
+        <v>0.07406338321347294</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2685158280878187</v>
+        <v>0.2685158458033682</v>
       </c>
       <c r="G61" t="n">
-        <v>63.42579140439093</v>
+        <v>63.4257922901684</v>
       </c>
     </row>
     <row r="62">
@@ -1842,22 +1842,22 @@
         <v>41305</v>
       </c>
       <c r="B62" t="n">
-        <v>0.5521878136034833</v>
+        <v>0.5521879766740614</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5521878136034833</v>
+        <v>-0.5521879766740614</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1088403659500817</v>
+        <v>0.1088396104689209</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2772100914875204</v>
+        <v>0.2772099026172302</v>
       </c>
       <c r="G62" t="n">
-        <v>63.86050457437602</v>
+        <v>63.86049513086152</v>
       </c>
     </row>
     <row r="63">
@@ -1865,22 +1865,22 @@
         <v>41333</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3832100837766666</v>
+        <v>0.3832090017644655</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.3832100837766666</v>
+        <v>-0.3832090017644655</v>
       </c>
       <c r="E63" t="n">
-        <v>0.452180024715489</v>
+        <v>0.4521803165072489</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3630450061788723</v>
+        <v>0.3630450791268122</v>
       </c>
       <c r="G63" t="n">
-        <v>68.15225030894361</v>
+        <v>68.15225395634062</v>
       </c>
     </row>
     <row r="64">
@@ -1888,22 +1888,22 @@
         <v>41364</v>
       </c>
       <c r="B64" t="n">
-        <v>0.4129727475015758</v>
+        <v>0.4129704597757733</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.4129727475015758</v>
+        <v>-0.4129704597757733</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3974415448310449</v>
+        <v>0.3974418423572721</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3493603862077612</v>
+        <v>0.349360460589318</v>
       </c>
       <c r="G64" t="n">
-        <v>67.46801931038806</v>
+        <v>67.46802302946591</v>
       </c>
     </row>
     <row r="65">
@@ -1911,22 +1911,22 @@
         <v>41394</v>
       </c>
       <c r="B65" t="n">
-        <v>0.5303798613344407</v>
+        <v>0.5303761995580267</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.5303798613344407</v>
+        <v>-0.5303761995580267</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4224135219214957</v>
+        <v>0.4224132700788999</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3556033804803739</v>
+        <v>0.355603317519725</v>
       </c>
       <c r="G65" t="n">
-        <v>67.78016902401869</v>
+        <v>67.78016587598626</v>
       </c>
     </row>
     <row r="66">
@@ -1934,22 +1934,22 @@
         <v>41425</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9777398588571673</v>
+        <v>0.9777350476321303</v>
       </c>
       <c r="C66" t="n">
         <v>-1</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9777398588571673</v>
+        <v>-0.9777350476321303</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1149512223896378</v>
+        <v>0.1149512833799435</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2212621944025905</v>
+        <v>-0.2212621791550141</v>
       </c>
       <c r="G66" t="n">
-        <v>38.93689027987048</v>
+        <v>38.93689104224929</v>
       </c>
     </row>
     <row r="67">
@@ -1957,22 +1957,22 @@
         <v>41455</v>
       </c>
       <c r="B67" t="n">
-        <v>0.8050359477128936</v>
+        <v>0.8050305369744665</v>
       </c>
       <c r="C67" t="n">
         <v>-1</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8050359477128936</v>
+        <v>-0.8050305369744665</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1437972934724853</v>
+        <v>0.1437970408488535</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2140506766318787</v>
+        <v>-0.2140507397877866</v>
       </c>
       <c r="G67" t="n">
-        <v>39.29746616840607</v>
+        <v>39.29746301061067</v>
       </c>
     </row>
     <row r="68">
@@ -1980,22 +1980,22 @@
         <v>41486</v>
       </c>
       <c r="B68" t="n">
-        <v>0.8478876696228324</v>
+        <v>0.8478812715832498</v>
       </c>
       <c r="C68" t="n">
         <v>-1</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8478876696228324</v>
+        <v>-0.8478812715832498</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3790725812026023</v>
+        <v>0.3790729069822095</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.1552318546993494</v>
+        <v>-0.1552317732544476</v>
       </c>
       <c r="G68" t="n">
-        <v>42.23840726503253</v>
+        <v>42.23841133727762</v>
       </c>
     </row>
     <row r="69">
@@ -2003,22 +2003,22 @@
         <v>41517</v>
       </c>
       <c r="B69" t="n">
-        <v>0.5689765567494039</v>
+        <v>0.5689731277705016</v>
       </c>
       <c r="C69" t="n">
         <v>-1</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.5689765567494039</v>
+        <v>-0.5689731277705016</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3880070767070931</v>
+        <v>0.3880071069949545</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.1529982308232267</v>
+        <v>-0.1529982232512614</v>
       </c>
       <c r="G69" t="n">
-        <v>42.35008845883866</v>
+        <v>42.35008883743693</v>
       </c>
     </row>
     <row r="70">
@@ -2026,22 +2026,22 @@
         <v>41547</v>
       </c>
       <c r="B70" t="n">
-        <v>0.5853998713206033</v>
+        <v>0.5853987311738877</v>
       </c>
       <c r="C70" t="n">
         <v>-1</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.5853998713206033</v>
+        <v>-0.5853987311738877</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5033760288156808</v>
+        <v>0.5033768625723065</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.1241559927960798</v>
+        <v>-0.1241557843569234</v>
       </c>
       <c r="G70" t="n">
-        <v>43.79220036019601</v>
+        <v>43.79221078215383</v>
       </c>
     </row>
     <row r="71">
@@ -2049,22 +2049,22 @@
         <v>41578</v>
       </c>
       <c r="B71" t="n">
-        <v>0.8892544436685994</v>
+        <v>0.8892538237317911</v>
       </c>
       <c r="C71" t="n">
         <v>-1</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8892544436685994</v>
+        <v>-0.8892538237317911</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3943574725576549</v>
+        <v>0.3943577597181614</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1514106318605863</v>
+        <v>-0.1514105600704597</v>
       </c>
       <c r="G71" t="n">
-        <v>42.42946840697068</v>
+        <v>42.42947199647702</v>
       </c>
     </row>
     <row r="72">
@@ -2081,13 +2081,13 @@
         <v>-1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4807703653326779</v>
+        <v>0.4807700705027558</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1298074086668305</v>
+        <v>-0.1298074823743111</v>
       </c>
       <c r="G72" t="n">
-        <v>43.50962956665848</v>
+        <v>43.50962588128445</v>
       </c>
     </row>
     <row r="73">
@@ -2104,13 +2104,13 @@
         <v>-1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4310499065910437</v>
+        <v>0.4310501844156813</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1422375233522391</v>
+        <v>-0.1422374538960797</v>
       </c>
       <c r="G73" t="n">
-        <v>42.88812383238805</v>
+        <v>42.88812730519602</v>
       </c>
     </row>
     <row r="74">
@@ -2118,22 +2118,22 @@
         <v>41670</v>
       </c>
       <c r="B74" t="n">
-        <v>0.6010310089526316</v>
+        <v>0.6010334611043162</v>
       </c>
       <c r="C74" t="n">
         <v>-1</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.6010310089526316</v>
+        <v>-0.6010334611043162</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6096780598761148</v>
+        <v>0.6096780352254815</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.0975804850309713</v>
+        <v>-0.09758049119362963</v>
       </c>
       <c r="G74" t="n">
-        <v>45.12097574845144</v>
+        <v>45.12097544031852</v>
       </c>
     </row>
     <row r="75">
@@ -2141,22 +2141,22 @@
         <v>41698</v>
       </c>
       <c r="B75" t="n">
-        <v>0.8039201044290348</v>
+        <v>0.8039215227861521</v>
       </c>
       <c r="C75" t="n">
         <v>-1</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.8039201044290348</v>
+        <v>-0.8039215227861521</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2390862615853299</v>
+        <v>0.239085975153582</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1902284346036675</v>
+        <v>-0.1902285062116045</v>
       </c>
       <c r="G75" t="n">
-        <v>40.48857826981662</v>
+        <v>40.48857468941978</v>
       </c>
     </row>
     <row r="76">
@@ -2164,22 +2164,22 @@
         <v>41729</v>
       </c>
       <c r="B76" t="n">
-        <v>0.6506351167104657</v>
+        <v>0.6506338219836373</v>
       </c>
       <c r="C76" t="n">
         <v>-1</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.6506351167104657</v>
+        <v>-0.6506338219836373</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2704011193828281</v>
+        <v>0.2704008423335076</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.182399720154293</v>
+        <v>-0.1823997894166231</v>
       </c>
       <c r="G76" t="n">
-        <v>40.88001399228535</v>
+        <v>40.88001052916884</v>
       </c>
     </row>
     <row r="77">
@@ -2187,22 +2187,22 @@
         <v>41759</v>
       </c>
       <c r="B77" t="n">
-        <v>0.6306202238900704</v>
+        <v>0.6306186660777446</v>
       </c>
       <c r="C77" t="n">
         <v>-1</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.6306202238900704</v>
+        <v>-0.6306186660777446</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03553965171684869</v>
+        <v>0.03554005279152179</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.2411150870707878</v>
+        <v>-0.2411149868021195</v>
       </c>
       <c r="G77" t="n">
-        <v>37.94424564646061</v>
+        <v>37.94425065989402</v>
       </c>
     </row>
     <row r="78">
@@ -2210,22 +2210,22 @@
         <v>41790</v>
       </c>
       <c r="B78" t="n">
-        <v>0.576124597079269</v>
+        <v>0.5761252896154735</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.576124597079269</v>
+        <v>-0.5761252896154735</v>
       </c>
       <c r="E78" t="n">
-        <v>0.09921116201034121</v>
+        <v>0.09921023184019757</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2748027905025853</v>
+        <v>0.2748025579600494</v>
       </c>
       <c r="G78" t="n">
-        <v>63.74013952512927</v>
+        <v>63.74012789800248</v>
       </c>
     </row>
     <row r="79">
@@ -2233,22 +2233,22 @@
         <v>41820</v>
       </c>
       <c r="B79" t="n">
-        <v>0.7244486680774359</v>
+        <v>0.7244470861316847</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.7244486680774359</v>
+        <v>-0.7244470861316847</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.06887402637624647</v>
+        <v>-0.06887427144830721</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2327814934059383</v>
+        <v>0.2327814321379232</v>
       </c>
       <c r="G79" t="n">
-        <v>61.63907467029692</v>
+        <v>61.63907160689616</v>
       </c>
     </row>
     <row r="80">
@@ -2256,22 +2256,22 @@
         <v>41851</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3438606218425948</v>
+        <v>0.3438588406523782</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.3438606218425948</v>
+        <v>-0.3438588406523782</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2228086629152292</v>
+        <v>0.2228087150323905</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3057021657288073</v>
+        <v>0.3057021787580976</v>
       </c>
       <c r="G80" t="n">
-        <v>65.28510828644036</v>
+        <v>65.28510893790488</v>
       </c>
     </row>
     <row r="81">
@@ -2279,22 +2279,22 @@
         <v>41882</v>
       </c>
       <c r="B81" t="n">
-        <v>0.7778599074131626</v>
+        <v>0.7778624543251826</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.7778599074131626</v>
+        <v>-0.7778624543251826</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3562861639538759</v>
+        <v>0.3562861958726782</v>
       </c>
       <c r="F81" t="n">
-        <v>0.339071540988469</v>
+        <v>0.3390715489681695</v>
       </c>
       <c r="G81" t="n">
-        <v>66.95357704942346</v>
+        <v>66.95357744840848</v>
       </c>
     </row>
     <row r="82">
@@ -2302,22 +2302,22 @@
         <v>41912</v>
       </c>
       <c r="B82" t="n">
-        <v>0.4784303309638653</v>
+        <v>0.478436646221439</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.4784303309638653</v>
+        <v>-0.478436646221439</v>
       </c>
       <c r="E82" t="n">
-        <v>0.474577691265854</v>
+        <v>0.4745777051515823</v>
       </c>
       <c r="F82" t="n">
-        <v>0.3686444228164635</v>
+        <v>0.3686444262878955</v>
       </c>
       <c r="G82" t="n">
-        <v>68.43222114082317</v>
+        <v>68.43222131439477</v>
       </c>
     </row>
     <row r="83">
@@ -2325,22 +2325,22 @@
         <v>41943</v>
       </c>
       <c r="B83" t="n">
-        <v>0.3855728822060733</v>
+        <v>0.3855697771385381</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.3855728822060733</v>
+        <v>-0.3855697771385381</v>
       </c>
       <c r="E83" t="n">
-        <v>0.5854759645601858</v>
+        <v>0.5854766038506433</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3963689911400464</v>
+        <v>0.3963691509626608</v>
       </c>
       <c r="G83" t="n">
-        <v>69.81844955700231</v>
+        <v>69.81845754813304</v>
       </c>
     </row>
     <row r="84">
@@ -2348,22 +2348,22 @@
         <v>41973</v>
       </c>
       <c r="B84" t="n">
-        <v>0.3832526716545966</v>
+        <v>0.3832542727196191</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.3832526716545966</v>
+        <v>-0.3832542727196191</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8797669922189842</v>
+        <v>0.8797675497914862</v>
       </c>
       <c r="F84" t="n">
-        <v>0.4699417480547461</v>
+        <v>0.4699418874478716</v>
       </c>
       <c r="G84" t="n">
-        <v>73.49708740273731</v>
+        <v>73.49709437239358</v>
       </c>
     </row>
     <row r="85">
@@ -2371,13 +2371,13 @@
         <v>42004</v>
       </c>
       <c r="B85" t="n">
-        <v>0.2832485997311141</v>
+        <v>0.2832522135344828</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.2832485997311141</v>
+        <v>-0.2832522135344828</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2394,13 +2394,13 @@
         <v>42035</v>
       </c>
       <c r="B86" t="n">
-        <v>0.2621783559741739</v>
+        <v>0.2621815394752641</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.2621783559741739</v>
+        <v>-0.2621815394752641</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -2417,13 +2417,13 @@
         <v>42063</v>
       </c>
       <c r="B87" t="n">
-        <v>0.3156800617781103</v>
+        <v>0.3156796204176329</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.3156800617781103</v>
+        <v>-0.3156796204176329</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -2440,13 +2440,13 @@
         <v>42094</v>
       </c>
       <c r="B88" t="n">
-        <v>0.1497245861169263</v>
+        <v>0.1497299402938097</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.1497245861169263</v>
+        <v>-0.1497299402938097</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -2463,13 +2463,13 @@
         <v>42124</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1982310032552878</v>
+        <v>0.1982267171197197</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.1982310032552878</v>
+        <v>-0.1982267171197197</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -2486,13 +2486,13 @@
         <v>42155</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1456765434550095</v>
+        <v>0.1456761796158479</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.1456765434550095</v>
+        <v>-0.1456761796158479</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -2509,13 +2509,13 @@
         <v>42185</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.1022739504078421</v>
+        <v>-0.102274679849558</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1022739504078421</v>
+        <v>0.102274679849558</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -2532,13 +2532,13 @@
         <v>42216</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1349787712166808</v>
+        <v>0.1349804347691064</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.1349787712166808</v>
+        <v>-0.1349804347691064</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -2555,13 +2555,13 @@
         <v>42247</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.3973745023361989</v>
+        <v>-0.3973723000675078</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3973745023361989</v>
+        <v>0.3973723000675078</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -2578,13 +2578,13 @@
         <v>42277</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.3858157778024258</v>
+        <v>-0.3858149892784157</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3858157778024258</v>
+        <v>0.3858149892784157</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2601,13 +2601,13 @@
         <v>42308</v>
       </c>
       <c r="B95" t="n">
-        <v>-0.1599154073700874</v>
+        <v>-0.1599161416891519</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1599154073700874</v>
+        <v>0.1599161416891519</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -2624,13 +2624,13 @@
         <v>42338</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.2451150258192877</v>
+        <v>-0.2451162753447806</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2451150258192877</v>
+        <v>0.2451162753447806</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -2647,22 +2647,22 @@
         <v>42369</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.3509296869371307</v>
+        <v>-0.3509325017411704</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3509296869371307</v>
+        <v>0.3509325017411704</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9270649622122249</v>
+        <v>0.9270649831915468</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4817662405530562</v>
+        <v>0.4817662457978867</v>
       </c>
       <c r="G97" t="n">
-        <v>74.08831202765282</v>
+        <v>74.08831228989435</v>
       </c>
     </row>
     <row r="98">
@@ -2670,22 +2670,22 @@
         <v>42400</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.4563052266035448</v>
+        <v>-0.4563074260143978</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4563052266035448</v>
+        <v>0.4563074260143978</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9120550299623522</v>
+        <v>0.9120547656219415</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4780137574905881</v>
+        <v>0.4780136914054854</v>
       </c>
       <c r="G98" t="n">
-        <v>73.9006878745294</v>
+        <v>73.90068457027427</v>
       </c>
     </row>
     <row r="99">
@@ -2693,22 +2693,22 @@
         <v>42429</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.7488359199607031</v>
+        <v>-0.7488318834667067</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0.7488359199607031</v>
+        <v>0.7488318834667067</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9880362912496399</v>
+        <v>0.9880358621159155</v>
       </c>
       <c r="F99" t="n">
-        <v>0.49700907281241</v>
+        <v>0.4970089655289789</v>
       </c>
       <c r="G99" t="n">
-        <v>74.8504536406205</v>
+        <v>74.85044827644894</v>
       </c>
     </row>
     <row r="100">
@@ -2716,22 +2716,22 @@
         <v>42460</v>
       </c>
       <c r="B100" t="n">
-        <v>-0.3039306209582812</v>
+        <v>-0.3039285443126603</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3039306209582812</v>
+        <v>0.3039285443126603</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7805431034231494</v>
+        <v>0.7805428029949112</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4451357758557873</v>
+        <v>0.4451357007487278</v>
       </c>
       <c r="G100" t="n">
-        <v>72.25678879278937</v>
+        <v>72.25678503743639</v>
       </c>
     </row>
     <row r="101">
@@ -2739,22 +2739,22 @@
         <v>42490</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.4061223116754205</v>
+        <v>-0.4061224356122011</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4061223116754205</v>
+        <v>0.4061224356122011</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6491000144837743</v>
+        <v>0.649099424391957</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4122750036209436</v>
+        <v>0.4122748560979893</v>
       </c>
       <c r="G101" t="n">
-        <v>70.61375018104718</v>
+        <v>70.61374280489946</v>
       </c>
     </row>
     <row r="102">
@@ -2762,22 +2762,22 @@
         <v>42521</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.3327254485320612</v>
+        <v>-0.3327254401256747</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3327254485320612</v>
+        <v>0.3327254401256747</v>
       </c>
       <c r="E102" t="n">
-        <v>0.5516670920669302</v>
+        <v>0.5516670770620198</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3879167730167326</v>
+        <v>0.3879167692655049</v>
       </c>
       <c r="G102" t="n">
-        <v>69.39583865083662</v>
+        <v>69.39583846327525</v>
       </c>
     </row>
     <row r="103">
@@ -2785,22 +2785,22 @@
         <v>42551</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.2382511138901809</v>
+        <v>-0.2382506788044925</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2382511138901809</v>
+        <v>0.2382506788044925</v>
       </c>
       <c r="E103" t="n">
-        <v>0.3892459125115739</v>
+        <v>0.3892454712859623</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3473114781278935</v>
+        <v>0.3473113678214906</v>
       </c>
       <c r="G103" t="n">
-        <v>67.36557390639467</v>
+        <v>67.36556839107453</v>
       </c>
     </row>
     <row r="104">
@@ -2808,22 +2808,22 @@
         <v>42582</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.1306900314939579</v>
+        <v>-0.1306895420105013</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1306900314939579</v>
+        <v>0.1306895420105013</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2239133419362755</v>
+        <v>0.2239136213358956</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3059783354840689</v>
+        <v>0.3059784053339739</v>
       </c>
       <c r="G104" t="n">
-        <v>65.29891677420345</v>
+        <v>65.2989202666987</v>
       </c>
     </row>
     <row r="105">
@@ -2831,22 +2831,22 @@
         <v>42613</v>
       </c>
       <c r="B105" t="n">
-        <v>0.289756352527264</v>
+        <v>0.2897564183638602</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.289756352527264</v>
+        <v>-0.2897564183638602</v>
       </c>
       <c r="E105" t="n">
-        <v>0.09820581798704786</v>
+        <v>0.09820586422841319</v>
       </c>
       <c r="F105" t="n">
-        <v>0.274551454496762</v>
+        <v>0.2745514660571033</v>
       </c>
       <c r="G105" t="n">
-        <v>63.7275727248381</v>
+        <v>63.72757330285517</v>
       </c>
     </row>
     <row r="106">
@@ -2854,22 +2854,22 @@
         <v>42643</v>
       </c>
       <c r="B106" t="n">
-        <v>0.2695207876063175</v>
+        <v>0.2695264866609443</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.2695207876063175</v>
+        <v>-0.2695264866609443</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.09455486084681654</v>
+        <v>-0.0945547895443513</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2263612847882959</v>
+        <v>0.2263613026139122</v>
       </c>
       <c r="G106" t="n">
-        <v>61.3180642394148</v>
+        <v>61.31806513069561</v>
       </c>
     </row>
     <row r="107">
@@ -2877,22 +2877,22 @@
         <v>42674</v>
       </c>
       <c r="B107" t="n">
-        <v>-0.2543678616607846</v>
+        <v>-0.2543647275628801</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2543678616607846</v>
+        <v>0.2543647275628801</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.08894599685950282</v>
+        <v>-0.08894563964873277</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2277635007851243</v>
+        <v>0.2277635900878168</v>
       </c>
       <c r="G107" t="n">
-        <v>61.38817503925622</v>
+        <v>61.38817950439084</v>
       </c>
     </row>
     <row r="108">
@@ -2900,22 +2900,22 @@
         <v>42704</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.005430526108636872</v>
+        <v>-0.005432916951593196</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0.005430526108636872</v>
+        <v>0.005432916951593196</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.4484666800765899</v>
+        <v>-0.4484662554185566</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1378833299808525</v>
+        <v>0.1378834361453609</v>
       </c>
       <c r="G108" t="n">
-        <v>56.89416649904263</v>
+        <v>56.89417180726804</v>
       </c>
     </row>
     <row r="109">
@@ -2923,22 +2923,22 @@
         <v>42735</v>
       </c>
       <c r="B109" t="n">
-        <v>0.2863297592161509</v>
+        <v>0.2863306372733518</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.2863297592161509</v>
+        <v>-0.2863306372733518</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.8804424064865564</v>
+        <v>-0.8804422402304259</v>
       </c>
       <c r="F109" t="n">
-        <v>0.02988939837836091</v>
+        <v>0.02988943994239351</v>
       </c>
       <c r="G109" t="n">
-        <v>51.49446991891804</v>
+        <v>51.49447199711967</v>
       </c>
     </row>
     <row r="110">
@@ -2946,13 +2946,13 @@
         <v>42766</v>
       </c>
       <c r="B110" t="n">
-        <v>0.7299763297910437</v>
+        <v>0.729975130696068</v>
       </c>
       <c r="C110" t="n">
         <v>-1</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.7299763297910437</v>
+        <v>-0.729975130696068</v>
       </c>
       <c r="E110" t="n">
         <v>-1</v>
@@ -2969,13 +2969,13 @@
         <v>42794</v>
       </c>
       <c r="B111" t="n">
-        <v>0.7089283833925143</v>
+        <v>0.7089272439586457</v>
       </c>
       <c r="C111" t="n">
         <v>-1</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.7089283833925143</v>
+        <v>-0.7089272439586457</v>
       </c>
       <c r="E111" t="n">
         <v>-1</v>
@@ -2992,22 +2992,22 @@
         <v>42825</v>
       </c>
       <c r="B112" t="n">
-        <v>0.4292660302510641</v>
+        <v>0.4292664470129884</v>
       </c>
       <c r="C112" t="n">
         <v>-1</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.4292660302510641</v>
+        <v>-0.4292664470129884</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.798426359472987</v>
+        <v>-0.7984266736746392</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.4496065898682468</v>
+        <v>-0.4496066684186598</v>
       </c>
       <c r="G112" t="n">
-        <v>27.51967050658766</v>
+        <v>27.51966657906701</v>
       </c>
     </row>
     <row r="113">
@@ -3015,22 +3015,22 @@
         <v>42855</v>
       </c>
       <c r="B113" t="n">
-        <v>0.4837133782267932</v>
+        <v>0.4837140205474229</v>
       </c>
       <c r="C113" t="n">
         <v>-1</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.4837133782267932</v>
+        <v>-0.4837140205474229</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.148864977984589</v>
+        <v>-0.1488649055164356</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.2872162444961472</v>
+        <v>-0.2872162263791089</v>
       </c>
       <c r="G113" t="n">
-        <v>35.63918777519264</v>
+        <v>35.63918868104455</v>
       </c>
     </row>
     <row r="114">
@@ -3038,22 +3038,22 @@
         <v>42886</v>
       </c>
       <c r="B114" t="n">
-        <v>0.449803090430026</v>
+        <v>0.4498032142666766</v>
       </c>
       <c r="C114" t="n">
         <v>-1</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.449803090430026</v>
+        <v>-0.4498032142666766</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.01850437300627004</v>
+        <v>-0.0185040210768512</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.2546260932515675</v>
+        <v>-0.2546260052692128</v>
       </c>
       <c r="G114" t="n">
-        <v>37.26869533742163</v>
+        <v>37.26869973653935</v>
       </c>
     </row>
     <row r="115">
@@ -3061,22 +3061,22 @@
         <v>42916</v>
       </c>
       <c r="B115" t="n">
-        <v>0.4606366591054505</v>
+        <v>0.4606378673009544</v>
       </c>
       <c r="C115" t="n">
         <v>-1</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.4606366591054505</v>
+        <v>-0.4606378673009544</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1851429759208702</v>
+        <v>0.1851430235108271</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.2037142560197824</v>
+        <v>-0.2037142441222932</v>
       </c>
       <c r="G115" t="n">
-        <v>39.81428719901088</v>
+        <v>39.81428779388534</v>
       </c>
     </row>
     <row r="116">
@@ -3084,22 +3084,22 @@
         <v>42947</v>
       </c>
       <c r="B116" t="n">
-        <v>0.3773790272101165</v>
+        <v>0.3773805359433051</v>
       </c>
       <c r="C116" t="n">
         <v>-1</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.3773790272101165</v>
+        <v>-0.3773805359433051</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.3747866903144558</v>
+        <v>-0.3747865931593341</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.343696672578614</v>
+        <v>-0.3436966482898335</v>
       </c>
       <c r="G116" t="n">
-        <v>32.8151663710693</v>
+        <v>32.81516758550832</v>
       </c>
     </row>
     <row r="117">
@@ -3107,22 +3107,22 @@
         <v>42978</v>
       </c>
       <c r="B117" t="n">
-        <v>0.3757405753396203</v>
+        <v>0.3757416093855719</v>
       </c>
       <c r="C117" t="n">
         <v>-1</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.3757405753396203</v>
+        <v>-0.3757416093855719</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.3300953977070161</v>
+        <v>-0.3300953064867755</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.3325238494267541</v>
+        <v>-0.3325238266216939</v>
       </c>
       <c r="G117" t="n">
-        <v>33.3738075286623</v>
+        <v>33.3738086689153</v>
       </c>
     </row>
     <row r="118">
@@ -3130,22 +3130,22 @@
         <v>43008</v>
       </c>
       <c r="B118" t="n">
-        <v>0.4963141991149894</v>
+        <v>0.4963086690338224</v>
       </c>
       <c r="C118" t="n">
         <v>-1</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.4963141991149894</v>
+        <v>-0.4963086690338224</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.1891676950891684</v>
+        <v>-0.1891670259068307</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.2972919237722921</v>
+        <v>-0.2972917564767077</v>
       </c>
       <c r="G118" t="n">
-        <v>35.13540381138539</v>
+        <v>35.13541217616461</v>
       </c>
     </row>
     <row r="119">
@@ -3153,22 +3153,22 @@
         <v>43039</v>
       </c>
       <c r="B119" t="n">
-        <v>0.8030326226014249</v>
+        <v>0.8030303374289494</v>
       </c>
       <c r="C119" t="n">
         <v>-1</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.8030326226014249</v>
+        <v>-0.8030303374289494</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.3444563264339708</v>
+        <v>-0.3444556419610573</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.3361140816084927</v>
+        <v>-0.3361139104902643</v>
       </c>
       <c r="G119" t="n">
-        <v>33.19429591957537</v>
+        <v>33.19430447548679</v>
       </c>
     </row>
     <row r="120">
@@ -3176,22 +3176,22 @@
         <v>43069</v>
       </c>
       <c r="B120" t="n">
-        <v>0.7313368478898306</v>
+        <v>0.7313396337156284</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.7313368478898306</v>
+        <v>-0.7313396337156284</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.2551295275381696</v>
+        <v>-0.2551294573786893</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1862176181154576</v>
+        <v>0.1862176356553277</v>
       </c>
       <c r="G120" t="n">
-        <v>59.31088090577288</v>
+        <v>59.31088178276638</v>
       </c>
     </row>
     <row r="121">
@@ -3199,22 +3199,22 @@
         <v>43100</v>
       </c>
       <c r="B121" t="n">
-        <v>0.6439715906334685</v>
+        <v>0.6439706235844724</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.6439715906334685</v>
+        <v>-0.6439706235844724</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.2754861252932329</v>
+        <v>-0.2754869099321281</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1811284686766917</v>
+        <v>0.181128272516968</v>
       </c>
       <c r="G121" t="n">
-        <v>59.0564234338346</v>
+        <v>59.0564136258484</v>
       </c>
     </row>
     <row r="122">
@@ -3222,22 +3222,22 @@
         <v>43131</v>
       </c>
       <c r="B122" t="n">
-        <v>0.8814558255022933</v>
+        <v>0.8814598479870371</v>
       </c>
       <c r="C122" t="n">
         <v>-1</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.8814558255022933</v>
+        <v>-0.8814598479870371</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.3769929724113797</v>
+        <v>-0.3769928800335925</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.344248243102845</v>
+        <v>-0.3442482200083982</v>
       </c>
       <c r="G122" t="n">
-        <v>32.78758784485775</v>
+        <v>32.78758899958009</v>
       </c>
     </row>
     <row r="123">
@@ -3245,22 +3245,22 @@
         <v>43159</v>
       </c>
       <c r="B123" t="n">
-        <v>0.2884960077153638</v>
+        <v>0.2884926357814975</v>
       </c>
       <c r="C123" t="n">
         <v>-1</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.2884960077153638</v>
+        <v>-0.2884926357814975</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.282979511983014</v>
+        <v>-0.2829797053854348</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.3207448779957535</v>
+        <v>-0.3207449263463587</v>
       </c>
       <c r="G123" t="n">
-        <v>33.96275610021232</v>
+        <v>33.96275368268207</v>
       </c>
     </row>
     <row r="124">
@@ -3268,22 +3268,22 @@
         <v>43190</v>
       </c>
       <c r="B124" t="n">
-        <v>0.1738277860966868</v>
+        <v>0.1738257319051383</v>
       </c>
       <c r="C124" t="n">
         <v>-1</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.1738277860966868</v>
+        <v>-0.1738257319051383</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.554701378088747</v>
+        <v>-0.5547009962064957</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.3886753445221868</v>
+        <v>-0.3886752490516239</v>
       </c>
       <c r="G124" t="n">
-        <v>30.56623277389066</v>
+        <v>30.56623754741881</v>
       </c>
     </row>
     <row r="125">
@@ -3291,22 +3291,22 @@
         <v>43220</v>
       </c>
       <c r="B125" t="n">
-        <v>0.1395897887385053</v>
+        <v>0.1395879764995875</v>
       </c>
       <c r="C125" t="n">
         <v>-1</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.1395897887385053</v>
+        <v>-0.1395879764995875</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.8183142394135237</v>
+        <v>-0.8183137851893204</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.4545785598533809</v>
+        <v>-0.4545784462973301</v>
       </c>
       <c r="G125" t="n">
-        <v>27.27107200733095</v>
+        <v>27.27107768513349</v>
       </c>
     </row>
     <row r="126">
@@ -3314,13 +3314,13 @@
         <v>43251</v>
       </c>
       <c r="B126" t="n">
-        <v>0.1624933753740008</v>
+        <v>0.1624967317004697</v>
       </c>
       <c r="C126" t="n">
         <v>-1</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.1624933753740008</v>
+        <v>-0.1624967317004697</v>
       </c>
       <c r="E126" t="n">
         <v>-1</v>
@@ -3337,22 +3337,22 @@
         <v>43281</v>
       </c>
       <c r="B127" t="n">
-        <v>0.2028979973742805</v>
+        <v>0.2028974125009248</v>
       </c>
       <c r="C127" t="n">
         <v>-1</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.2028979973742805</v>
+        <v>-0.2028974125009248</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.9646368427506588</v>
+        <v>-0.9646367536465257</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.4911592106876647</v>
+        <v>-0.4911591884116314</v>
       </c>
       <c r="G127" t="n">
-        <v>25.44203946561677</v>
+        <v>25.44204057941843</v>
       </c>
     </row>
     <row r="128">
@@ -3360,22 +3360,22 @@
         <v>43312</v>
       </c>
       <c r="B128" t="n">
-        <v>0.2852715698037918</v>
+        <v>0.2852669653222206</v>
       </c>
       <c r="C128" t="n">
         <v>-1</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.2852715698037918</v>
+        <v>-0.2852669653222206</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.6986842355294195</v>
+        <v>-0.6986834398666993</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.4246710588823549</v>
+        <v>-0.4246708599666749</v>
       </c>
       <c r="G128" t="n">
-        <v>28.76644705588226</v>
+        <v>28.76645700166626</v>
       </c>
     </row>
     <row r="129">
@@ -3383,22 +3383,22 @@
         <v>43343</v>
       </c>
       <c r="B129" t="n">
-        <v>0.4714244996433808</v>
+        <v>0.4714284960937252</v>
       </c>
       <c r="C129" t="n">
         <v>-1</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.4714244996433808</v>
+        <v>-0.4714284960937252</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.651403415880294</v>
+        <v>-0.6514033017738765</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.4128508539700735</v>
+        <v>-0.4128508254434691</v>
       </c>
       <c r="G129" t="n">
-        <v>29.35745730149632</v>
+        <v>29.35745872782655</v>
       </c>
     </row>
     <row r="130">
@@ -3406,22 +3406,22 @@
         <v>43373</v>
       </c>
       <c r="B130" t="n">
-        <v>0.3818410296702609</v>
+        <v>0.3818431251940572</v>
       </c>
       <c r="C130" t="n">
         <v>-1</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.3818410296702609</v>
+        <v>-0.3818431251940572</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.7190357031293871</v>
+        <v>-0.7190368807521293</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.4297589257823468</v>
+        <v>-0.4297592201880324</v>
       </c>
       <c r="G130" t="n">
-        <v>28.51205371088266</v>
+        <v>28.51203899059838</v>
       </c>
     </row>
     <row r="131">
@@ -3429,22 +3429,22 @@
         <v>43404</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.2278167133284522</v>
+        <v>-0.2278173553544968</v>
       </c>
       <c r="C131" t="n">
         <v>-1</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2278167133284522</v>
+        <v>0.2278173553544968</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.2712440722634438</v>
+        <v>-0.2712442959962667</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.3178110180658609</v>
+        <v>-0.3178110739990667</v>
       </c>
       <c r="G131" t="n">
-        <v>34.10944909670695</v>
+        <v>34.10944630004666</v>
       </c>
     </row>
     <row r="132">
@@ -3452,22 +3452,22 @@
         <v>43434</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.2842792650042066</v>
+        <v>-0.2842762403444231</v>
       </c>
       <c r="C132" t="n">
         <v>-1</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2842792650042066</v>
+        <v>0.2842762403444231</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2262043505531956</v>
+        <v>0.2262038050921553</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.1934489123617011</v>
+        <v>-0.1934490487269612</v>
       </c>
       <c r="G132" t="n">
-        <v>40.32755438191494</v>
+        <v>40.32754756365195</v>
       </c>
     </row>
     <row r="133">
@@ -3475,22 +3475,22 @@
         <v>43465</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.891037883042496</v>
+        <v>-0.8910396612737783</v>
       </c>
       <c r="C133" t="n">
         <v>-1</v>
       </c>
       <c r="D133" t="n">
-        <v>0.891037883042496</v>
+        <v>0.8910396612737783</v>
       </c>
       <c r="E133" t="n">
-        <v>0.4496856237495168</v>
+        <v>0.4496866491529257</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.1375785940626208</v>
+        <v>-0.1375783377117686</v>
       </c>
       <c r="G133" t="n">
-        <v>43.12107029686896</v>
+        <v>43.12108311441158</v>
       </c>
     </row>
     <row r="134">
@@ -3498,22 +3498,22 @@
         <v>43496</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.7668713647823872</v>
+        <v>-0.7668740329328503</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0.7668713647823872</v>
+        <v>0.7668740329328503</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2998045884951204</v>
+        <v>0.2998045989244624</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3249511471237801</v>
+        <v>0.3249511497311156</v>
       </c>
       <c r="G134" t="n">
-        <v>66.24755735618901</v>
+        <v>66.24755748655578</v>
       </c>
     </row>
     <row r="135">
@@ -3521,22 +3521,22 @@
         <v>43524</v>
       </c>
       <c r="B135" t="n">
-        <v>-0.3757333759844713</v>
+        <v>-0.3757292218734297</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3757333759844713</v>
+        <v>0.3757292218734297</v>
       </c>
       <c r="E135" t="n">
-        <v>0.071885606044002</v>
+        <v>0.07188591214015576</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2679714015110005</v>
+        <v>0.267971478035039</v>
       </c>
       <c r="G135" t="n">
-        <v>63.39857007555003</v>
+        <v>63.39857390175194</v>
       </c>
     </row>
     <row r="136">
@@ -3544,22 +3544,22 @@
         <v>43555</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.1002086025112549</v>
+        <v>-0.1002047875172375</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1002086025112549</v>
+        <v>0.1002047875172375</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1774820284190736</v>
+        <v>0.1774818029101123</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2943705071047684</v>
+        <v>0.2943704507275281</v>
       </c>
       <c r="G136" t="n">
-        <v>64.71852535523843</v>
+        <v>64.7185225363764</v>
       </c>
     </row>
     <row r="137">
@@ -3567,22 +3567,22 @@
         <v>43585</v>
       </c>
       <c r="B137" t="n">
-        <v>0.1154520186943851</v>
+        <v>0.1154554613354823</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.1154520186943851</v>
+        <v>-0.1154554613354823</v>
       </c>
       <c r="E137" t="n">
-        <v>0.2620990024639672</v>
+        <v>0.2620990361965331</v>
       </c>
       <c r="F137" t="n">
-        <v>0.3155247506159918</v>
+        <v>0.3155247590491333</v>
       </c>
       <c r="G137" t="n">
-        <v>65.77623753079959</v>
+        <v>65.77623795245667</v>
       </c>
     </row>
     <row r="138">
@@ -3590,22 +3590,22 @@
         <v>43616</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.4434939501167779</v>
+        <v>-0.443498787775886</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>0.4434939501167779</v>
+        <v>0.443498787775886</v>
       </c>
       <c r="E138" t="n">
-        <v>0.5893554189822291</v>
+        <v>0.5893553532348811</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3973388547455573</v>
+        <v>0.3973388383087203</v>
       </c>
       <c r="G138" t="n">
-        <v>69.86694273727787</v>
+        <v>69.86694191543602</v>
       </c>
     </row>
     <row r="139">
@@ -3613,22 +3613,22 @@
         <v>43646</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.06013669600888082</v>
+        <v>-0.06013386821014212</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0.06013669600888082</v>
+        <v>0.06013386821014212</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3273696359598009</v>
+        <v>0.327369889891772</v>
       </c>
       <c r="F139" t="n">
-        <v>0.3318424089899502</v>
+        <v>0.331842472472943</v>
       </c>
       <c r="G139" t="n">
-        <v>66.59212044949751</v>
+        <v>66.59212362364715</v>
       </c>
     </row>
     <row r="140">
@@ -3636,22 +3636,22 @@
         <v>43677</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.2036829459521066</v>
+        <v>-0.203681297563984</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>0.2036829459521066</v>
+        <v>0.203681297563984</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3193690578101936</v>
+        <v>0.3193690867812885</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3298422644525484</v>
+        <v>0.3298422716953221</v>
       </c>
       <c r="G140" t="n">
-        <v>66.49211322262742</v>
+        <v>66.4921135847661</v>
       </c>
     </row>
     <row r="141">
@@ -3659,22 +3659,22 @@
         <v>43708</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.4952697290291083</v>
+        <v>-0.4952697126132397</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4952697290291083</v>
+        <v>0.4952697126132397</v>
       </c>
       <c r="E141" t="n">
-        <v>0.5207509170069858</v>
+        <v>0.5207514105192058</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3801877292517465</v>
+        <v>0.3801878526298015</v>
       </c>
       <c r="G141" t="n">
-        <v>69.00938646258732</v>
+        <v>69.00939263149007</v>
       </c>
     </row>
     <row r="142">
@@ -3682,22 +3682,22 @@
         <v>43738</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.4155169773521743</v>
+        <v>-0.4155171342713689</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4155169773521743</v>
+        <v>0.4155171342713689</v>
       </c>
       <c r="E142" t="n">
-        <v>0.5929388656187067</v>
+        <v>0.5929392837991191</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3982347164046767</v>
+        <v>0.3982348209497798</v>
       </c>
       <c r="G142" t="n">
-        <v>69.91173582023383</v>
+        <v>69.91174104748899</v>
       </c>
     </row>
     <row r="143">
@@ -3705,22 +3705,22 @@
         <v>43769</v>
       </c>
       <c r="B143" t="n">
-        <v>0.1772755197176602</v>
+        <v>0.1772761408431658</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.1772755197176602</v>
+        <v>-0.1772761408431658</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3011990650025461</v>
+        <v>0.3011990634811846</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3252997662506365</v>
+        <v>0.3252997658702961</v>
       </c>
       <c r="G143" t="n">
-        <v>66.26498831253183</v>
+        <v>66.2649882935148</v>
       </c>
     </row>
     <row r="144">
@@ -3728,22 +3728,22 @@
         <v>43799</v>
       </c>
       <c r="B144" t="n">
-        <v>0.3368026835401541</v>
+        <v>0.3368002942957482</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.3368026835401541</v>
+        <v>-0.3368002942957482</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.101993221539738</v>
+        <v>-0.1019925409582417</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2245016946150655</v>
+        <v>0.2245018647604396</v>
       </c>
       <c r="G144" t="n">
-        <v>61.22508473075327</v>
+        <v>61.22509323802198</v>
       </c>
     </row>
     <row r="145">
@@ -3760,13 +3760,13 @@
         <v>-1</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.5546813032312741</v>
+        <v>-0.5546805052611606</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1113296741921815</v>
+        <v>0.1113298736847098</v>
       </c>
       <c r="G145" t="n">
-        <v>55.56648370960907</v>
+        <v>55.5664936842355</v>
       </c>
     </row>
     <row r="146">
@@ -3774,22 +3774,22 @@
         <v>43861</v>
       </c>
       <c r="B146" t="n">
-        <v>0.5909266081672554</v>
+        <v>0.5909298866852478</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.5909266081672554</v>
+        <v>-0.5909298866852478</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1760555858030105</v>
+        <v>0.1760558804049211</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2940138964507526</v>
+        <v>0.2940139701012303</v>
       </c>
       <c r="G146" t="n">
-        <v>64.70069482253763</v>
+        <v>64.70069850506151</v>
       </c>
     </row>
     <row r="147">
@@ -3797,22 +3797,22 @@
         <v>43890</v>
       </c>
       <c r="B147" t="n">
-        <v>-0.2094496202401305</v>
+        <v>-0.2094497630880024</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2094496202401305</v>
+        <v>0.2094497630880024</v>
       </c>
       <c r="E147" t="n">
-        <v>0.4759182924188182</v>
+        <v>0.4759176494753046</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3689795731047045</v>
+        <v>0.3689794123688261</v>
       </c>
       <c r="G147" t="n">
-        <v>68.44897865523522</v>
+        <v>68.44897061844131</v>
       </c>
     </row>
     <row r="148">
@@ -3843,13 +3843,13 @@
         <v>43951</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.5316951219698263</v>
+        <v>-0.5316966214689192</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>0.5316951219698263</v>
+        <v>0.5316966214689192</v>
       </c>
       <c r="E149" t="n">
         <v>1</v>
@@ -3866,22 +3866,22 @@
         <v>43982</v>
       </c>
       <c r="B150" t="n">
-        <v>0.1292260049356416</v>
+        <v>0.1292300943645774</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.1292260049356416</v>
+        <v>-0.1292300943645774</v>
       </c>
       <c r="E150" t="n">
-        <v>0.82362361887463</v>
+        <v>0.8236241198343336</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4559059047186574</v>
+        <v>0.4559060299585834</v>
       </c>
       <c r="G150" t="n">
-        <v>72.79529523593287</v>
+        <v>72.79530149792916</v>
       </c>
     </row>
     <row r="151">
@@ -3889,22 +3889,22 @@
         <v>44012</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.2549242486435401</v>
+        <v>-0.2549235518282252</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>0.2549242486435401</v>
+        <v>0.2549235518282252</v>
       </c>
       <c r="E151" t="n">
-        <v>0.7415268894781476</v>
+        <v>0.7415262631578582</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4353817223695369</v>
+        <v>0.4353815657894645</v>
       </c>
       <c r="G151" t="n">
-        <v>71.76908611847685</v>
+        <v>71.76907828947323</v>
       </c>
     </row>
     <row r="152">
@@ -3912,22 +3912,22 @@
         <v>44043</v>
       </c>
       <c r="B152" t="n">
-        <v>0.2125924859070487</v>
+        <v>0.2125933781468126</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.2125924859070487</v>
+        <v>-0.2125933781468126</v>
       </c>
       <c r="E152" t="n">
-        <v>0.4809809859984314</v>
+        <v>0.480980640897483</v>
       </c>
       <c r="F152" t="n">
-        <v>0.3702452464996078</v>
+        <v>0.3702451602243708</v>
       </c>
       <c r="G152" t="n">
-        <v>68.51226232498038</v>
+        <v>68.51225801121853</v>
       </c>
     </row>
     <row r="153">
@@ -3935,22 +3935,22 @@
         <v>44074</v>
       </c>
       <c r="B153" t="n">
-        <v>0.7385660294031787</v>
+        <v>0.7385611085329065</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.7385660294031787</v>
+        <v>-0.7385611085329065</v>
       </c>
       <c r="E153" t="n">
-        <v>0.200342178510152</v>
+        <v>0.2003421647614406</v>
       </c>
       <c r="F153" t="n">
-        <v>0.300085544627538</v>
+        <v>0.3000855411903601</v>
       </c>
       <c r="G153" t="n">
-        <v>65.00427723137689</v>
+        <v>65.00427705951802</v>
       </c>
     </row>
     <row r="154">
@@ -3958,22 +3958,22 @@
         <v>44104</v>
       </c>
       <c r="B154" t="n">
-        <v>0.5048067465123661</v>
+        <v>0.5048078077821534</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.5048067465123661</v>
+        <v>-0.5048078077821534</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3828248090282613</v>
+        <v>0.3828245065660481</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3457062022570653</v>
+        <v>0.345706126641512</v>
       </c>
       <c r="G154" t="n">
-        <v>67.28531011285325</v>
+        <v>67.28530633207561</v>
       </c>
     </row>
     <row r="155">
@@ -3981,22 +3981,22 @@
         <v>44135</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.06969639647952014</v>
+        <v>-0.06969766852221551</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>0.06969639647952014</v>
+        <v>0.06969766852221551</v>
       </c>
       <c r="E155" t="n">
-        <v>0.6744123433317434</v>
+        <v>0.6744125545962883</v>
       </c>
       <c r="F155" t="n">
-        <v>0.4186030858329358</v>
+        <v>0.4186031386490721</v>
       </c>
       <c r="G155" t="n">
-        <v>70.9301542916468</v>
+        <v>70.9301569324536</v>
       </c>
     </row>
     <row r="156">
@@ -4004,22 +4004,22 @@
         <v>44165</v>
       </c>
       <c r="B156" t="n">
-        <v>0.5168871523547388</v>
+        <v>0.5168879696840296</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.5168871523547388</v>
+        <v>-0.5168879696840296</v>
       </c>
       <c r="E156" t="n">
-        <v>0.2214647783204046</v>
+        <v>0.2214647606455068</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3053661945801011</v>
+        <v>0.3053661901613767</v>
       </c>
       <c r="G156" t="n">
-        <v>65.26830972900505</v>
+        <v>65.26830950806884</v>
       </c>
     </row>
     <row r="157">
@@ -4027,22 +4027,22 @@
         <v>44196</v>
       </c>
       <c r="B157" t="n">
-        <v>0.5050457970259344</v>
+        <v>0.5050452475197742</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.5050457970259344</v>
+        <v>-0.5050452475197742</v>
       </c>
       <c r="E157" t="n">
-        <v>0.293720323694956</v>
+        <v>0.2937208886278868</v>
       </c>
       <c r="F157" t="n">
-        <v>0.323430080923739</v>
+        <v>0.3234302221569717</v>
       </c>
       <c r="G157" t="n">
-        <v>66.17150404618695</v>
+        <v>66.17151110784857</v>
       </c>
     </row>
     <row r="158">
@@ -4050,22 +4050,22 @@
         <v>44227</v>
       </c>
       <c r="B158" t="n">
-        <v>0.4508700930528733</v>
+        <v>0.4508659645861297</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.4508700930528733</v>
+        <v>-0.4508659645861297</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.2882861612047909</v>
+        <v>-0.2882864294926665</v>
       </c>
       <c r="F158" t="n">
-        <v>0.1779284596988023</v>
+        <v>0.1779283926268334</v>
       </c>
       <c r="G158" t="n">
-        <v>58.89642298494011</v>
+        <v>58.89641963134167</v>
       </c>
     </row>
     <row r="159">
@@ -4280,13 +4280,13 @@
         <v>44530</v>
       </c>
       <c r="B168" t="n">
-        <v>0.8511426119261823</v>
+        <v>0.8511395486878108</v>
       </c>
       <c r="C168" t="n">
         <v>-1</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.8511426119261823</v>
+        <v>-0.8511395486878108</v>
       </c>
       <c r="E168" t="n">
         <v>-1</v>
@@ -4326,13 +4326,13 @@
         <v>44592</v>
       </c>
       <c r="B170" t="n">
-        <v>0.4618565981996479</v>
+        <v>0.4618568549821793</v>
       </c>
       <c r="C170" t="n">
         <v>-1</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.4618565981996479</v>
+        <v>-0.4618568549821793</v>
       </c>
       <c r="E170" t="n">
         <v>-1</v>
@@ -4349,13 +4349,13 @@
         <v>44620</v>
       </c>
       <c r="B171" t="n">
-        <v>0.1780681941987146</v>
+        <v>0.17807133110318</v>
       </c>
       <c r="C171" t="n">
         <v>-1</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.1780681941987146</v>
+        <v>-0.17807133110318</v>
       </c>
       <c r="E171" t="n">
         <v>-1</v>
@@ -4372,13 +4372,13 @@
         <v>44651</v>
       </c>
       <c r="B172" t="n">
-        <v>0.07001597416442971</v>
+        <v>0.0700147542622597</v>
       </c>
       <c r="C172" t="n">
         <v>-1</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.07001597416442971</v>
+        <v>-0.0700147542622597</v>
       </c>
       <c r="E172" t="n">
         <v>-1</v>
@@ -4395,13 +4395,13 @@
         <v>44681</v>
       </c>
       <c r="B173" t="n">
-        <v>-0.6536862725519565</v>
+        <v>-0.6536828517098715</v>
       </c>
       <c r="C173" t="n">
         <v>-1</v>
       </c>
       <c r="D173" t="n">
-        <v>0.6536862725519565</v>
+        <v>0.6536828517098715</v>
       </c>
       <c r="E173" t="n">
         <v>-1</v>
@@ -4418,13 +4418,13 @@
         <v>44712</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.669981711867113</v>
+        <v>-0.6699860682895256</v>
       </c>
       <c r="C174" t="n">
         <v>-1</v>
       </c>
       <c r="D174" t="n">
-        <v>0.669981711867113</v>
+        <v>0.6699860682895256</v>
       </c>
       <c r="E174" t="n">
         <v>-1</v>
@@ -4464,13 +4464,13 @@
         <v>44773</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.9067331770288718</v>
+        <v>-0.9067354748466913</v>
       </c>
       <c r="C176" t="n">
         <v>-1</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9067331770288718</v>
+        <v>0.9067354748466913</v>
       </c>
       <c r="E176" t="n">
         <v>-1</v>
@@ -4519,13 +4519,13 @@
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.5179999986345991</v>
+        <v>-0.5179995553398034</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.3794999996586498</v>
+        <v>-0.3794998888349508</v>
       </c>
       <c r="G178" t="n">
-        <v>31.02500001706751</v>
+        <v>31.02500555825246</v>
       </c>
     </row>
     <row r="179">
@@ -4542,13 +4542,13 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.511036083715925</v>
+        <v>-0.5110364907243988</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.3777590209289813</v>
+        <v>-0.3777591226810997</v>
       </c>
       <c r="G179" t="n">
-        <v>31.11204895355094</v>
+        <v>31.11204386594502</v>
       </c>
     </row>
     <row r="180">
@@ -4588,13 +4588,13 @@
         <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.5989552243790301</v>
+        <v>-0.5989547049384584</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.3997388060947575</v>
+        <v>-0.3997386762346146</v>
       </c>
       <c r="G181" t="n">
-        <v>30.01305969526212</v>
+        <v>30.01306618826927</v>
       </c>
     </row>
     <row r="182">
@@ -4611,13 +4611,13 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.3055267476541731</v>
+        <v>-0.3055271312537798</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.3263816869135433</v>
+        <v>-0.326381782813445</v>
       </c>
       <c r="G182" t="n">
-        <v>33.68091565432284</v>
+        <v>33.68091085932775</v>
       </c>
     </row>
     <row r="183">
@@ -4634,13 +4634,13 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>0.1273672996050453</v>
+        <v>0.1273673047794588</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.2181581750987387</v>
+        <v>-0.2181581738051353</v>
       </c>
       <c r="G183" t="n">
-        <v>39.09209124506307</v>
+        <v>39.09209130974324</v>
       </c>
     </row>
     <row r="184">
@@ -4657,13 +4657,13 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0.448084492021296</v>
+        <v>0.4480844785304436</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.137978876994676</v>
+        <v>-0.1379788803673891</v>
       </c>
       <c r="G184" t="n">
-        <v>43.1010561502662</v>
+        <v>43.10105598163054</v>
       </c>
     </row>
     <row r="185">
@@ -4671,22 +4671,22 @@
         <v>45046</v>
       </c>
       <c r="B185" t="n">
-        <v>-0.7751571022816153</v>
+        <v>-0.7751607125782197</v>
       </c>
       <c r="C185" t="n">
         <v>-1</v>
       </c>
       <c r="D185" t="n">
-        <v>0.7751571022816153</v>
+        <v>0.7751607125782197</v>
       </c>
       <c r="E185" t="n">
-        <v>0.6816524879075884</v>
+        <v>0.6816527605859962</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.07958687802310291</v>
+        <v>-0.07958680985350092</v>
       </c>
       <c r="G185" t="n">
-        <v>46.02065609884485</v>
+        <v>46.02065950732496</v>
       </c>
     </row>
     <row r="186">
@@ -4694,22 +4694,22 @@
         <v>45077</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.5674423617276769</v>
+        <v>-0.5674413240084193</v>
       </c>
       <c r="C186" t="n">
         <v>-1</v>
       </c>
       <c r="D186" t="n">
-        <v>0.5674423617276769</v>
+        <v>0.5674413240084193</v>
       </c>
       <c r="E186" t="n">
-        <v>0.9984256691439025</v>
+        <v>0.998425333021095</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.0003935827140243708</v>
+        <v>-0.0003936667447262399</v>
       </c>
       <c r="G186" t="n">
-        <v>49.98032086429878</v>
+        <v>49.98031666276369</v>
       </c>
     </row>
     <row r="187">
@@ -4717,22 +4717,22 @@
         <v>45107</v>
       </c>
       <c r="B187" t="n">
-        <v>0.3357862111056159</v>
+        <v>0.3357878886059921</v>
       </c>
       <c r="C187" t="n">
         <v>-1</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.3357862111056159</v>
+        <v>-0.3357878886059921</v>
       </c>
       <c r="E187" t="n">
-        <v>0.6629255378352946</v>
+        <v>0.6629255571060531</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.08426861554117634</v>
+        <v>-0.08426861072348674</v>
       </c>
       <c r="G187" t="n">
-        <v>45.78656922294118</v>
+        <v>45.78656946382566</v>
       </c>
     </row>
     <row r="188">
@@ -4740,22 +4740,22 @@
         <v>45138</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.04924585882379926</v>
+        <v>-0.0492448132126791</v>
       </c>
       <c r="C188" t="n">
         <v>-1</v>
       </c>
       <c r="D188" t="n">
-        <v>0.04924585882379926</v>
+        <v>0.0492448132126791</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3043036699719792</v>
+        <v>0.3043033609558827</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.1739240825070052</v>
+        <v>-0.1739241597610293</v>
       </c>
       <c r="G188" t="n">
-        <v>41.30379587464974</v>
+        <v>41.30379201194854</v>
       </c>
     </row>
     <row r="189">
@@ -4763,22 +4763,22 @@
         <v>45169</v>
       </c>
       <c r="B189" t="n">
-        <v>0.09564440856161512</v>
+        <v>0.09564879387952756</v>
       </c>
       <c r="C189" t="n">
         <v>-1</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.09564440856161512</v>
+        <v>-0.09564879387952756</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2618957436422258</v>
+        <v>0.2618960544091042</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.1845260640894436</v>
+        <v>-0.1845259863977239</v>
       </c>
       <c r="G189" t="n">
-        <v>40.77369679552783</v>
+        <v>40.7737006801138</v>
       </c>
     </row>
     <row r="190">
@@ -4786,22 +4786,22 @@
         <v>45199</v>
       </c>
       <c r="B190" t="n">
-        <v>0.3018556115430632</v>
+        <v>0.3018555588190914</v>
       </c>
       <c r="C190" t="n">
         <v>-1</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.3018556115430632</v>
+        <v>-0.3018555588190914</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.02668360823287819</v>
+        <v>-0.02668394128567194</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.2566709020582195</v>
+        <v>-0.256670985321418</v>
       </c>
       <c r="G190" t="n">
-        <v>37.16645489708903</v>
+        <v>37.1664507339291</v>
       </c>
     </row>
     <row r="191">
@@ -4809,22 +4809,22 @@
         <v>45230</v>
       </c>
       <c r="B191" t="n">
-        <v>-0.2628824273689599</v>
+        <v>-0.2628845158903402</v>
       </c>
       <c r="C191" t="n">
         <v>-1</v>
       </c>
       <c r="D191" t="n">
-        <v>0.2628824273689599</v>
+        <v>0.2628845158903402</v>
       </c>
       <c r="E191" t="n">
-        <v>0.1862858291997603</v>
+        <v>0.1862858318688103</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.2034285427000599</v>
+        <v>-0.2034285420327974</v>
       </c>
       <c r="G191" t="n">
-        <v>39.828572864997</v>
+        <v>39.82857289836013</v>
       </c>
     </row>
     <row r="192">
@@ -4832,22 +4832,22 @@
         <v>45260</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.06022840437629199</v>
+        <v>-0.06023062596501431</v>
       </c>
       <c r="C192" t="n">
         <v>-1</v>
       </c>
       <c r="D192" t="n">
-        <v>0.06022840437629199</v>
+        <v>0.06023062596501431</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3313990058601781</v>
+        <v>0.331399000397904</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.1671502485349555</v>
+        <v>-0.167150249900524</v>
       </c>
       <c r="G192" t="n">
-        <v>41.64248757325223</v>
+        <v>41.6424875049738</v>
       </c>
     </row>
     <row r="193">
@@ -4855,22 +4855,22 @@
         <v>45291</v>
       </c>
       <c r="B193" t="n">
-        <v>0.6254878519153165</v>
+        <v>0.6254882877996222</v>
       </c>
       <c r="C193" t="n">
         <v>-1</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.6254878519153165</v>
+        <v>-0.6254882877996222</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3195724087333729</v>
+        <v>0.3195724038961943</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.1701068978166568</v>
+        <v>-0.1701068990259514</v>
       </c>
       <c r="G193" t="n">
-        <v>41.49465510916716</v>
+        <v>41.49465504870243</v>
       </c>
     </row>
     <row r="194">
@@ -4878,22 +4878,22 @@
         <v>45322</v>
       </c>
       <c r="B194" t="n">
-        <v>0.3159024280025869</v>
+        <v>0.3159010177501089</v>
       </c>
       <c r="C194" t="n">
         <v>-1</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.3159024280025869</v>
+        <v>-0.3159010177501089</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3360623520522596</v>
+        <v>0.3360623462608839</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.1659844119869351</v>
+        <v>-0.165984413434779</v>
       </c>
       <c r="G194" t="n">
-        <v>41.70077940065325</v>
+        <v>41.70077932826105</v>
       </c>
     </row>
     <row r="195">
@@ -4901,22 +4901,22 @@
         <v>45351</v>
       </c>
       <c r="B195" t="n">
-        <v>0.8833758062416416</v>
+        <v>0.883376440239574</v>
       </c>
       <c r="C195" t="n">
         <v>-1</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.8833758062416416</v>
+        <v>-0.883376440239574</v>
       </c>
       <c r="E195" t="n">
-        <v>0.2866783237493731</v>
+        <v>0.2866783206777943</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.1783304190626567</v>
+        <v>-0.1783304198305514</v>
       </c>
       <c r="G195" t="n">
-        <v>41.08347904686717</v>
+        <v>41.08347900847243</v>
       </c>
     </row>
     <row r="196">
@@ -4924,22 +4924,22 @@
         <v>45382</v>
       </c>
       <c r="B196" t="n">
-        <v>0.9664521823444268</v>
+        <v>0.9664517140853696</v>
       </c>
       <c r="C196" t="n">
         <v>-1</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.9664521823444268</v>
+        <v>-0.9664517140853696</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.01467479819970579</v>
+        <v>-0.01467441127387244</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.2536686995499264</v>
+        <v>-0.2536686028184681</v>
       </c>
       <c r="G196" t="n">
-        <v>37.31656502250368</v>
+        <v>37.3165698590766</v>
       </c>
     </row>
     <row r="197">
@@ -4947,22 +4947,22 @@
         <v>45412</v>
       </c>
       <c r="B197" t="n">
-        <v>0.4067944709292441</v>
+        <v>0.4067932155260843</v>
       </c>
       <c r="C197" t="n">
         <v>-1</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.4067944709292441</v>
+        <v>-0.4067932155260843</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.0774881896174929</v>
+        <v>-0.0774878119597177</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.2693720474043732</v>
+        <v>-0.2693719529899294</v>
       </c>
       <c r="G197" t="n">
-        <v>36.53139762978134</v>
+        <v>36.53140235050353</v>
       </c>
     </row>
     <row r="198">
@@ -4970,22 +4970,22 @@
         <v>45443</v>
       </c>
       <c r="B198" t="n">
-        <v>0.6481180644128142</v>
+        <v>0.6481191691820873</v>
       </c>
       <c r="C198" t="n">
         <v>-1</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.6481180644128142</v>
+        <v>-0.6481191691820873</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.2376268903995719</v>
+        <v>-0.2376264555450114</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.309406722599893</v>
+        <v>-0.3094066138862528</v>
       </c>
       <c r="G198" t="n">
-        <v>34.52966387000535</v>
+        <v>34.52966930568736</v>
       </c>
     </row>
     <row r="199">
@@ -4993,22 +4993,22 @@
         <v>45473</v>
       </c>
       <c r="B199" t="n">
-        <v>0.5939538450247402</v>
+        <v>0.5939471093554748</v>
       </c>
       <c r="C199" t="n">
         <v>-1</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.5939538450247402</v>
+        <v>-0.5939471093554748</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.2108134965337405</v>
+        <v>-0.2108134780086329</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.3027033741334351</v>
+        <v>-0.3027033695021582</v>
       </c>
       <c r="G199" t="n">
-        <v>34.86483129332824</v>
+        <v>34.86483152489209</v>
       </c>
     </row>
     <row r="200">
@@ -5016,22 +5016,22 @@
         <v>45504</v>
       </c>
       <c r="B200" t="n">
-        <v>0.3847580886053642</v>
+        <v>0.3847574792853881</v>
       </c>
       <c r="C200" t="n">
         <v>-1</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.3847580886053642</v>
+        <v>-0.3847574792853881</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2506411827464734</v>
+        <v>0.2506411636804503</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.1873397043133816</v>
+        <v>-0.1873397090798875</v>
       </c>
       <c r="G200" t="n">
-        <v>40.63301478433092</v>
+        <v>40.63301454600563</v>
       </c>
     </row>
     <row r="201">
@@ -5039,22 +5039,22 @@
         <v>45535</v>
       </c>
       <c r="B201" t="n">
-        <v>0.6464727867105342</v>
+        <v>0.6464719281885505</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.6464727867105342</v>
+        <v>-0.6464719281885505</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3348139324827769</v>
+        <v>0.3348139210116098</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3337034831206942</v>
+        <v>0.3337034802529024</v>
       </c>
       <c r="G201" t="n">
-        <v>66.68517415603471</v>
+        <v>66.68517401264512</v>
       </c>
     </row>
     <row r="202">
@@ -5071,13 +5071,13 @@
         <v>-1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3624294000466574</v>
+        <v>0.3624297083799097</v>
       </c>
       <c r="F202" t="n">
-        <v>0.3406073500116644</v>
+        <v>0.3406074270949774</v>
       </c>
       <c r="G202" t="n">
-        <v>67.03036750058322</v>
+        <v>67.03037135474888</v>
       </c>
     </row>
     <row r="203">
@@ -5094,13 +5094,13 @@
         <v>-1</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2459076157383074</v>
+        <v>0.2459079450496706</v>
       </c>
       <c r="F203" t="n">
-        <v>0.3114769039345768</v>
+        <v>0.3114769862624177</v>
       </c>
       <c r="G203" t="n">
-        <v>65.57384519672884</v>
+        <v>65.57384931312087</v>
       </c>
     </row>
     <row r="204">
@@ -5117,13 +5117,13 @@
         <v>-1</v>
       </c>
       <c r="E204" t="n">
-        <v>0.2211881206557014</v>
+        <v>0.221188111895837</v>
       </c>
       <c r="F204" t="n">
-        <v>0.3052970301639253</v>
+        <v>0.3052970279739592</v>
       </c>
       <c r="G204" t="n">
-        <v>65.26485150819626</v>
+        <v>65.26485139869797</v>
       </c>
     </row>
     <row r="205">
@@ -5131,22 +5131,22 @@
         <v>45657</v>
       </c>
       <c r="B205" t="n">
-        <v>0.5583156119856647</v>
+        <v>0.5583144587275931</v>
       </c>
       <c r="C205" t="n">
         <v>-1</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.5583156119856647</v>
+        <v>-0.5583144587275931</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.0121356053184233</v>
+        <v>-0.01213560103416989</v>
       </c>
       <c r="F205" t="n">
-        <v>-0.2530339013296058</v>
+        <v>-0.2530339002585425</v>
       </c>
       <c r="G205" t="n">
-        <v>37.34830493351971</v>
+        <v>37.34830498707288</v>
       </c>
     </row>
     <row r="206">
@@ -5154,22 +5154,22 @@
         <v>45688</v>
       </c>
       <c r="B206" t="n">
-        <v>0.5973304527974895</v>
+        <v>0.5973304928206524</v>
       </c>
       <c r="C206" t="n">
         <v>-1</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.5973304527974895</v>
+        <v>-0.5973304928206524</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.03650869140932936</v>
+        <v>-0.03650868577054649</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.2591271728523323</v>
+        <v>-0.2591271714426366</v>
       </c>
       <c r="G206" t="n">
-        <v>37.04364135738339</v>
+        <v>37.04364142786817</v>
       </c>
     </row>
     <row r="207">
@@ -5177,22 +5177,22 @@
         <v>45716</v>
       </c>
       <c r="B207" t="n">
-        <v>0.1757793731836468</v>
+        <v>0.1757791536365912</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.1757793731836468</v>
+        <v>-0.1757791536365912</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.100189169665097</v>
+        <v>-0.1001891604731226</v>
       </c>
       <c r="F207" t="n">
-        <v>0.2249527075837257</v>
+        <v>0.2249527098817194</v>
       </c>
       <c r="G207" t="n">
-        <v>61.24763537918628</v>
+        <v>61.24763549408597</v>
       </c>
     </row>
     <row r="208">
@@ -5200,22 +5200,22 @@
         <v>45747</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.4276600415972277</v>
+        <v>-0.4276610682935648</v>
       </c>
       <c r="C208" t="n">
         <v>-1</v>
       </c>
       <c r="D208" t="n">
-        <v>0.4276600415972277</v>
+        <v>0.4276610682935648</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.01778699403899107</v>
+        <v>-0.0177869894650424</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.2544467485097477</v>
+        <v>-0.2544467473662606</v>
       </c>
       <c r="G208" t="n">
-        <v>37.27766257451262</v>
+        <v>37.27766263168697</v>
       </c>
     </row>
     <row r="209">
@@ -5223,22 +5223,22 @@
         <v>45777</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.3173172953023464</v>
+        <v>-0.3173159130805087</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3173172953023464</v>
+        <v>0.3173159130805087</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4430628451366215</v>
+        <v>0.443062501951635</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3607657112841554</v>
+        <v>0.3607656254879087</v>
       </c>
       <c r="G209" t="n">
-        <v>68.03828556420777</v>
+        <v>68.03828127439544</v>
       </c>
     </row>
     <row r="210">
@@ -5246,22 +5246,22 @@
         <v>45808</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.1182432806334594</v>
+        <v>-0.1182413606179633</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>0.1182432806334594</v>
+        <v>0.1182413606179633</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3943181991226453</v>
+        <v>0.3943181824689139</v>
       </c>
       <c r="F210" t="n">
-        <v>0.3485795497806613</v>
+        <v>0.3485795456172285</v>
       </c>
       <c r="G210" t="n">
-        <v>67.42897748903307</v>
+        <v>67.42897728086142</v>
       </c>
     </row>
     <row r="211">
@@ -5269,22 +5269,22 @@
         <v>45838</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.05314261934843294</v>
+        <v>-0.05314362324336672</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>0.05314261934843294</v>
+        <v>0.05314362324336672</v>
       </c>
       <c r="E211" t="n">
-        <v>0.167144956621109</v>
+        <v>0.1671446005819383</v>
       </c>
       <c r="F211" t="n">
-        <v>0.2917862391552772</v>
+        <v>0.2917861501454846</v>
       </c>
       <c r="G211" t="n">
-        <v>64.58931195776387</v>
+        <v>64.58930750727423</v>
       </c>
     </row>
     <row r="212">
@@ -5292,22 +5292,22 @@
         <v>45869</v>
       </c>
       <c r="B212" t="n">
-        <v>0.1622238966939956</v>
+        <v>0.162226049489215</v>
       </c>
       <c r="C212" t="n">
         <v>-1</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.1622238966939956</v>
+        <v>-0.162226049489215</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.1824037269098642</v>
+        <v>-0.1824041158647328</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.295600931727466</v>
+        <v>-0.2956010289661832</v>
       </c>
       <c r="G212" t="n">
-        <v>35.2199534136267</v>
+        <v>35.21994855169084</v>
       </c>
     </row>
     <row r="213">
@@ -5315,22 +5315,22 @@
         <v>45900</v>
       </c>
       <c r="B213" t="n">
-        <v>0.1013469657401947</v>
+        <v>0.1013442770050506</v>
       </c>
       <c r="C213" t="n">
         <v>-1</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.1013469657401947</v>
+        <v>-0.1013442770050506</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.1280236292714688</v>
+        <v>-0.1280236135270311</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.2820059073178672</v>
+        <v>-0.2820059033817578</v>
       </c>
       <c r="G213" t="n">
-        <v>35.89970463410664</v>
+        <v>35.89970483091211</v>
       </c>
     </row>
     <row r="214">
@@ -5338,22 +5338,22 @@
         <v>45930</v>
       </c>
       <c r="B214" t="n">
-        <v>0.1687321212079488</v>
+        <v>0.1687318574569109</v>
       </c>
       <c r="C214" t="n">
         <v>-1</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.1687321212079488</v>
+        <v>-0.1687318574569109</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.1485236996779091</v>
+        <v>-0.1485236828236414</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.2871309249194773</v>
+        <v>-0.2871309207059103</v>
       </c>
       <c r="G214" t="n">
-        <v>35.64345375402613</v>
+        <v>35.64345396470448</v>
       </c>
     </row>
     <row r="215">
@@ -5361,22 +5361,22 @@
         <v>45961</v>
       </c>
       <c r="B215" t="n">
-        <v>0.2310427309497884</v>
+        <v>0.2310420311671685</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.2310427309497884</v>
+        <v>-0.2310420311671685</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.1917014210624619</v>
+        <v>-0.1917014018473765</v>
       </c>
       <c r="F215" t="n">
-        <v>0.2020746447343845</v>
+        <v>0.2020746495381559</v>
       </c>
       <c r="G215" t="n">
-        <v>60.10373223671923</v>
+        <v>60.10373247690779</v>
       </c>
     </row>
     <row r="216">
@@ -5384,22 +5384,22 @@
         <v>45991</v>
       </c>
       <c r="B216" t="n">
-        <v>0.005976803080494747</v>
+        <v>0.005976714749267202</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.005976803080494747</v>
+        <v>-0.005976714749267202</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.2650874195298131</v>
+        <v>-0.2650873962894966</v>
       </c>
       <c r="F216" t="n">
-        <v>0.1837281451175467</v>
+        <v>0.1837281509276258</v>
       </c>
       <c r="G216" t="n">
-        <v>59.18640725587734</v>
+        <v>59.18640754638129</v>
       </c>
     </row>
     <row r="217">
@@ -5407,22 +5407,22 @@
         <v>46022</v>
       </c>
       <c r="B217" t="n">
-        <v>0.1379640918599567</v>
+        <v>0.1379641007143206</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.1379640918599567</v>
+        <v>-0.1379641007143206</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.241641258455685</v>
+        <v>-0.2416412365374364</v>
       </c>
       <c r="F217" t="n">
-        <v>0.1895896853860787</v>
+        <v>0.1895896908656409</v>
       </c>
       <c r="G217" t="n">
-        <v>59.47948426930394</v>
+        <v>59.47948454328205</v>
       </c>
     </row>
     <row r="218">
@@ -5430,22 +5430,22 @@
         <v>46053</v>
       </c>
       <c r="B218" t="n">
-        <v>0.04685666485050042</v>
+        <v>0.0468590110087036</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.04685666485050042</v>
+        <v>-0.0468590110087036</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.4885610964612435</v>
+        <v>-0.4885610609582454</v>
       </c>
       <c r="F218" t="n">
-        <v>0.1278597258846891</v>
+        <v>0.1278597347604387</v>
       </c>
       <c r="G218" t="n">
-        <v>56.39298629423446</v>
+        <v>56.39298673802193</v>
       </c>
     </row>
     <row r="219">
@@ -5453,22 +5453,22 @@
         <v>46081</v>
       </c>
       <c r="B219" t="n">
-        <v>0.2239912666201547</v>
+        <v>0.2239893820357645</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.2239912666201547</v>
+        <v>-0.2239893820357645</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.5809804678694205</v>
+        <v>-0.5809804273427234</v>
       </c>
       <c r="F219" t="n">
-        <v>0.1047548830326449</v>
+        <v>0.1047548931643192</v>
       </c>
       <c r="G219" t="n">
-        <v>55.23774415163224</v>
+        <v>55.23774465821596</v>
       </c>
     </row>
     <row r="220">
@@ -5476,13 +5476,13 @@
         <v>46112</v>
       </c>
       <c r="B220" t="n">
-        <v>0.1654935631955197</v>
+        <v>0.1654935346992432</v>
       </c>
       <c r="C220" t="n">
         <v>-1</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.1654935631955197</v>
+        <v>-0.1654935346992432</v>
       </c>
       <c r="E220" t="n">
         <v>-1</v>
